--- a/SPC26S1 - 06 June.xlsx
+++ b/SPC26S1 - 06 June.xlsx
@@ -2968,7 +2968,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="95">
+  <dxfs count="103">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3938,6 +3938,62 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9F9F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4A0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -7936,6 +7992,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -12795,6 +12877,32 @@
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="15">
       <formula>$N2=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="16">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="17">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="18">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="19">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="20">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -14921,6 +15029,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A17" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -18043,6 +18177,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A25" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -20146,6 +20306,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="95" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -20161,7 +20347,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -20336,7 +20522,127 @@
         <v>514</v>
       </c>
     </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row colours by Claim Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="45" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each claim row is shaded by its Claim Status (column A) using conditional formatting, so the colour follows the status automatically when it is changed. Rows with no Claim Status keep their normal formatting. The deadline countdown columns keep their own colour bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAID - green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Finalized - blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Received - lavender</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pending - yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Under Review - orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied - red</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Rejected - pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Not found - grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any other status is left unshaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="95" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="expression" dxfId="96" priority="2">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="expression" dxfId="97" priority="3">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="98" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="99" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" dxfId="100" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="expression" dxfId="101" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="expression" dxfId="102" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 06 June.xlsx
+++ b/SPC26S1 - 06 June.xlsx
@@ -2735,7 +2735,7 @@
     <t>136 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim goes to the bottom even when its Latest Date Worked is empty). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -9188,45 +9188,49 @@
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>46217</v>
+      </c>
       <c r="D11" s="4">
-        <v>564672683</v>
+        <v>562140958</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F11" s="6">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>263</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="11">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>246</v>
-      </c>
-      <c r="M11" s="11" t="str">
+        <v>243</v>
+      </c>
+      <c r="M11" s="11">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N11" s="11" t="str">
+        <v>282</v>
+      </c>
+      <c r="N11" s="11">
         <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="O11" s="6">
-        <v>46546</v>
+        <v>46543</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>49</v>
@@ -9247,28 +9251,30 @@
         <v>48</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="Z11" s="7">
-        <v>18176.900000000001</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA11" s="7">
-        <v>0</v>
+        <v>31016.19</v>
       </c>
       <c r="AB11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="6"/>
+        <v>4252.7299999999996</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>46217</v>
+      </c>
       <c r="AD11" s="7">
-        <v>18176.900000000001</v>
+        <v>1084.8800000000001</v>
       </c>
       <c r="AE11" s="4">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AF11" s="5" t="s">
         <v>102</v>
@@ -9276,15 +9282,17 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="4"/>
+      <c r="AJ11" s="4">
+        <v>564721141</v>
+      </c>
       <c r="AK11" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AM11" s="6">
-        <v>46211</v>
+        <v>46185</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>179</v>
@@ -9295,13 +9303,13 @@
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4">
-        <v>562699568</v>
+        <v>564672683</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F12" s="6">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>263</v>
@@ -9310,15 +9318,15 @@
         <v>263</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="11">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M12" s="11" t="str">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
@@ -9329,7 +9337,7 @@
         <v/>
       </c>
       <c r="O12" s="6">
-        <v>46547</v>
+        <v>46546</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>49</v>
@@ -9350,15 +9358,15 @@
         <v>48</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="Z12" s="7">
-        <v>5492.55</v>
+        <v>18176.900000000001</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -9368,26 +9376,26 @@
       </c>
       <c r="AC12" s="6"/>
       <c r="AD12" s="7">
-        <v>5492.55</v>
+        <v>18176.900000000001</v>
       </c>
       <c r="AE12" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="AM12" s="6">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>179</v>
@@ -9396,45 +9404,43 @@
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="3">
-        <v>46211</v>
-      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="4">
-        <v>563177256</v>
+        <v>562699568</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="F13" s="6">
-        <v>46192</v>
+        <v>46182</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>432</v>
+        <v>263</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>263</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>432</v>
+        <v>127</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="11">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>257</v>
-      </c>
-      <c r="M13" s="11">
+        <v>247</v>
+      </c>
+      <c r="M13" s="11" t="str">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>276</v>
-      </c>
-      <c r="N13" s="11">
+        <v/>
+      </c>
+      <c r="N13" s="11" t="str">
         <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
-        <v>31</v>
+        <v/>
       </c>
       <c r="O13" s="6">
-        <v>46557</v>
+        <v>46547</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>49</v>
@@ -9455,50 +9461,44 @@
         <v>48</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Z13" s="7">
-        <v>36353.800000000003</v>
+        <v>5492.55</v>
       </c>
       <c r="AA13" s="7">
-        <v>29931.31</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="7">
-        <v>5337.61</v>
-      </c>
-      <c r="AC13" s="6">
-        <v>46211</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="7">
-        <v>1084.8800000000001</v>
+        <v>5492.55</v>
       </c>
       <c r="AE13" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>537</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="4" t="s">
-        <v>538</v>
-      </c>
+      <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AM13" s="6">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>179</v>
@@ -9507,43 +9507,45 @@
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3">
+        <v>46211</v>
+      </c>
       <c r="D14" s="4">
-        <v>563203416</v>
+        <v>563177256</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="F14" s="6">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>263</v>
+        <v>432</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>263</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>134</v>
+        <v>432</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="11">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>260</v>
-      </c>
-      <c r="M14" s="11" t="str">
+        <v>257</v>
+      </c>
+      <c r="M14" s="11">
         <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N14" s="11" t="str">
+        <v>276</v>
+      </c>
+      <c r="N14" s="11">
         <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="O14" s="6">
-        <v>46560</v>
+        <v>46557</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>49</v>
@@ -9564,41 +9566,47 @@
         <v>48</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>36353.800000000003</v>
+      </c>
+      <c r="AA14" s="7">
+        <v>29931.31</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>5337.61</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>46211</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>1084.8800000000001</v>
+      </c>
+      <c r="AE14" s="4">
         <v>50</v>
       </c>
-      <c r="Z14" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AA14" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AE14" s="4">
-        <v>47</v>
-      </c>
       <c r="AF14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG14" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>537</v>
+      </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="4"/>
+      <c r="AJ14" s="4" t="s">
+        <v>538</v>
+      </c>
       <c r="AK14" s="5" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="AM14" s="6">
         <v>46196</v>
@@ -9608,31 +9616,33 @@
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="3">
-        <v>46268</v>
+        <v>46211</v>
       </c>
       <c r="D15" s="4">
-        <v>563163093</v>
+        <v>563164453</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>434</v>
+        <v>286</v>
       </c>
       <c r="F15" s="6">
         <v>46195</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>263</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="11">
@@ -9641,11 +9651,11 @@
       </c>
       <c r="M15" s="11">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="N15" s="11">
         <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="O15" s="6">
         <v>46560</v>
@@ -9669,7 +9679,7 @@
         <v>48</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
@@ -9680,13 +9690,13 @@
         <v>36353.800000000003</v>
       </c>
       <c r="AA15" s="7">
-        <v>29931.31</v>
+        <v>31016.19</v>
       </c>
       <c r="AB15" s="7">
-        <v>5337.61</v>
+        <v>4252.7299999999996</v>
       </c>
       <c r="AC15" s="6">
-        <v>46268</v>
+        <v>46211</v>
       </c>
       <c r="AD15" s="7">
         <v>1084.8800000000001</v>
@@ -9698,14 +9708,14 @@
         <v>102</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>539</v>
+        <v>223</v>
       </c>
       <c r="AH15" s="5" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="4" t="s">
-        <v>540</v>
+      <c r="AJ15" s="4">
+        <v>566076337</v>
       </c>
       <c r="AK15" s="5" t="s">
         <v>270</v>
@@ -9723,17 +9733,15 @@
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="3">
-        <v>46209</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="4">
-        <v>564042566</v>
+        <v>563203416</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F16" s="6">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>263</v>
@@ -9742,26 +9750,26 @@
         <v>263</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="11">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>262</v>
-      </c>
-      <c r="M16" s="11">
+        <v>260</v>
+      </c>
+      <c r="M16" s="11" t="str">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>274</v>
-      </c>
-      <c r="N16" s="11">
+        <v/>
+      </c>
+      <c r="N16" s="11" t="str">
         <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="O16" s="6">
-        <v>46562</v>
+        <v>46560</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>49</v>
@@ -9790,7 +9798,7 @@
         <v>50</v>
       </c>
       <c r="Z16" s="7">
-        <v>7792.75</v>
+        <v>6392.96</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -9798,32 +9806,28 @@
       <c r="AB16" s="7">
         <v>0</v>
       </c>
-      <c r="AC16" s="6">
-        <v>46209</v>
-      </c>
+      <c r="AC16" s="6"/>
       <c r="AD16" s="7">
-        <v>7792.75</v>
+        <v>6392.96</v>
       </c>
       <c r="AE16" s="4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>291</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AM16" s="6">
-        <v>46204</v>
+        <v>46196</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>179</v>
@@ -9832,18 +9836,20 @@
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3">
+        <v>46268</v>
+      </c>
       <c r="D17" s="4">
-        <v>564112414</v>
+        <v>563163093</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>292</v>
+        <v>434</v>
       </c>
       <c r="F17" s="6">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>263</v>
+        <v>151</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>263</v>
@@ -9852,23 +9858,23 @@
         <v>151</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="11">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>264</v>
-      </c>
-      <c r="M17" s="11" t="str">
+        <v>260</v>
+      </c>
+      <c r="M17" s="11">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N17" s="11" t="str">
+        <v>333</v>
+      </c>
+      <c r="N17" s="11">
         <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
-        <v/>
+        <v>88</v>
       </c>
       <c r="O17" s="6">
-        <v>46564</v>
+        <v>46560</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>49</v>
@@ -9894,41 +9900,47 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="Z17" s="7">
-        <v>2958.2</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA17" s="7">
-        <v>0</v>
+        <v>29931.31</v>
       </c>
       <c r="AB17" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="6"/>
+        <v>5337.61</v>
+      </c>
+      <c r="AC17" s="6">
+        <v>46268</v>
+      </c>
       <c r="AD17" s="7">
-        <v>2958.2</v>
+        <v>1084.8800000000001</v>
       </c>
       <c r="AE17" s="4">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AF17" s="5" t="s">
         <v>102</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="AH17" s="5"/>
+        <v>539</v>
+      </c>
+      <c r="AH17" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="4"/>
+      <c r="AJ17" s="4" t="s">
+        <v>540</v>
+      </c>
       <c r="AK17" s="5" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="AM17" s="6">
-        <v>46205</v>
+        <v>46196</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>179</v>
@@ -9938,16 +9950,16 @@
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
-        <v>46224</v>
+        <v>46209</v>
       </c>
       <c r="D18" s="4">
-        <v>565309736</v>
+        <v>564042566</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F18" s="6">
-        <v>46202</v>
+        <v>46197</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>263</v>
@@ -9956,26 +9968,26 @@
         <v>263</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="11">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M18" s="11">
         <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="N18" s="11">
         <f ca="1">IF($C18="","",$C18+120-TODAY())</f>
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="O18" s="6">
-        <v>46567</v>
+        <v>46562</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>49</v>
@@ -10004,7 +10016,7 @@
         <v>50</v>
       </c>
       <c r="Z18" s="7">
-        <v>6392.96</v>
+        <v>7792.75</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -10013,26 +10025,28 @@
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46224</v>
+        <v>46209</v>
       </c>
       <c r="AD18" s="7">
-        <v>6392.96</v>
+        <v>7792.75</v>
       </c>
       <c r="AE18" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG18" s="5"/>
+        <v>290</v>
+      </c>
+      <c r="AG18" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AM18" s="6">
         <v>46204</v>
@@ -10042,60 +10056,74 @@
       </c>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>566</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4">
-        <v>562142694</v>
+        <v>564112414</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F19" s="6">
-        <v>46177</v>
+        <v>46199</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="11" t="str">
+      <c r="L19" s="11">
         <f ca="1">IF($O19="","",$O19-TODAY())</f>
+        <v>264</v>
+      </c>
+      <c r="M19" s="11" t="str">
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
+      <c r="N19" s="11" t="str">
+        <f ca="1">IF($C19="","",$C19+120-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O19" s="6">
+        <v>46564</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="Q19" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V19" s="5" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="Z19" s="7">
-        <v>9479.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -10105,30 +10133,28 @@
       </c>
       <c r="AC19" s="6"/>
       <c r="AD19" s="7">
-        <v>9479.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AE19" s="4">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="AH19" s="5" t="s">
-        <v>300</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AM19" s="6">
-        <v>46185</v>
+        <v>46205</v>
       </c>
       <c r="AN19" s="5" t="s">
         <v>179</v>
@@ -10136,87 +10162,107 @@
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="C20" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="3">
+        <v>46219</v>
+      </c>
       <c r="D20" s="4">
-        <v>564106191</v>
+        <v>564117213</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F20" s="6">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>156</v>
+        <v>295</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="11" t="str">
+      <c r="L20" s="11">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="5"/>
+        <v>267</v>
+      </c>
+      <c r="M20" s="11">
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <v>284</v>
+      </c>
+      <c r="N20" s="11">
+        <f ca="1">IF($C20="","",$C20+120-TODAY())</f>
+        <v>39</v>
+      </c>
+      <c r="O20" s="6">
+        <v>46567</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="Q20" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V20" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
       <c r="Y20" s="5" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="Z20" s="7">
-        <v>2958.2</v>
+        <v>11832.8</v>
       </c>
       <c r="AA20" s="7">
-        <v>0</v>
+        <v>10095.450000000001</v>
       </c>
       <c r="AB20" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="6"/>
+        <v>1384.23</v>
+      </c>
+      <c r="AC20" s="6">
+        <v>46219</v>
+      </c>
       <c r="AD20" s="7">
-        <v>2958.2</v>
+        <v>353.12</v>
       </c>
       <c r="AE20" s="4">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AF20" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG20" s="5" t="s">
-        <v>176</v>
-      </c>
+      <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="4"/>
+      <c r="AJ20" s="4">
+        <v>567247169</v>
+      </c>
       <c r="AK20" s="5" t="s">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="AM20" s="6">
         <v>46205</v>
@@ -10226,59 +10272,53 @@
       </c>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="3">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="D21" s="4">
-        <v>564111540</v>
+        <v>565309736</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>170</v>
+        <v>296</v>
       </c>
       <c r="F21" s="6">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="3">
-        <v>46254</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="K21" s="3"/>
       <c r="L21" s="11">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-41</v>
+        <v>267</v>
       </c>
       <c r="M21" s="11">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="N21" s="11">
-        <f ca="1">IF($C21="","",$C21+90-TODAY())</f>
-        <v>1</v>
+        <f ca="1">IF($C21="","",$C21+120-TODAY())</f>
+        <v>44</v>
       </c>
       <c r="O21" s="6">
-        <v>46259</v>
+        <v>46567</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="R21" s="5" t="s">
         <v>49</v>
@@ -10287,21 +10327,21 @@
         <v>48</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="U21" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V21" s="5" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Z21" s="7">
-        <v>36353.800000000003</v>
+        <v>6392.96</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -10310,31 +10350,29 @@
         <v>0</v>
       </c>
       <c r="AC21" s="6">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="AD21" s="7">
-        <v>36353.800000000003</v>
+        <v>6392.96</v>
       </c>
       <c r="AE21" s="4">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG21" s="5" t="s">
-        <v>176</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>177</v>
+        <v>270</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>178</v>
+        <v>271</v>
       </c>
       <c r="AM21" s="6">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>179</v>
@@ -10342,73 +10380,51 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>564</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="3">
-        <v>46239</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="4">
-        <v>562698907</v>
+        <v>562142694</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="F22" s="6">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="3">
-        <v>46270</v>
-      </c>
-      <c r="L22" s="11">
+        <v>298</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="11" t="str">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-28</v>
-      </c>
-      <c r="M22" s="11">
-        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>119</v>
-      </c>
-      <c r="N22" s="11">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>304</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46272</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="5"/>
       <c r="Q22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U22" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
       <c r="V22" s="5" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
@@ -10416,7 +10432,7 @@
         <v>50</v>
       </c>
       <c r="Z22" s="7">
-        <v>6392.96</v>
+        <v>9479.4</v>
       </c>
       <c r="AA22" s="7">
         <v>0</v>
@@ -10424,32 +10440,32 @@
       <c r="AB22" s="7">
         <v>0</v>
       </c>
-      <c r="AC22" s="6">
-        <v>46202</v>
-      </c>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="7">
-        <v>6392.96</v>
+        <v>9479.4</v>
       </c>
       <c r="AE22" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="AH22" s="5"/>
+        <v>299</v>
+      </c>
+      <c r="AH22" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>203</v>
+        <v>301</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="AM22" s="6">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="AN22" s="5" t="s">
         <v>179</v>
@@ -10457,71 +10473,49 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>564</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="3">
-        <v>46217</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="4">
-        <v>563172458</v>
+        <v>564106191</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>217</v>
+        <v>297</v>
       </c>
       <c r="F23" s="6">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="K23" s="3">
-        <v>46262</v>
-      </c>
-      <c r="L23" s="11">
+        <v>209</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="11" t="str">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M23" s="11">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>97</v>
-      </c>
-      <c r="N23" s="11">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>282</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46281</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
       <c r="V23" s="5" t="s">
         <v>174</v>
       </c>
@@ -10544,82 +10538,84 @@
         <v>2958.2</v>
       </c>
       <c r="AE23" s="4">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG23" s="5"/>
+      <c r="AG23" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="AM23" s="6">
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>518</v>
+        <v>169</v>
       </c>
       <c r="C24" s="3">
-        <v>46220</v>
+        <v>46211</v>
       </c>
       <c r="D24" s="4">
-        <v>564043829</v>
+        <v>564111540</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="F24" s="6">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="K24" s="3">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L24" s="11">
         <f ca="1">IF($O24="","",$O24-TODAY())</f>
-        <v>-14</v>
+        <v>-41</v>
       </c>
       <c r="M24" s="11">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="N24" s="11">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($C24="","",$C24+90-TODAY())</f>
+        <v>1</v>
       </c>
       <c r="O24" s="6">
-        <v>46286</v>
+        <v>46259</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="R24" s="5" t="s">
         <v>49</v>
@@ -10628,21 +10624,21 @@
         <v>48</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V24" s="5" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
       <c r="Y24" s="5" t="s">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="Z24" s="7">
-        <v>9479.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA24" s="7">
         <v>0</v>
@@ -10651,29 +10647,31 @@
         <v>0</v>
       </c>
       <c r="AC24" s="6">
-        <v>46220</v>
+        <v>46211</v>
       </c>
       <c r="AD24" s="7">
-        <v>9479.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE24" s="4">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AF24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG24" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="AL24" s="5" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="AM24" s="6">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="AN24" s="5" t="s">
         <v>179</v>
@@ -10683,26 +10681,26 @@
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>519</v>
+      <c r="B25" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="C25" s="3">
-        <v>46220</v>
+        <v>46239</v>
       </c>
       <c r="D25" s="4">
-        <v>564053524</v>
+        <v>562698907</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="F25" s="6">
-        <v>46202</v>
+        <v>46182</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>43</v>
@@ -10711,31 +10709,31 @@
         <v>199</v>
       </c>
       <c r="K25" s="3">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="L25" s="11">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="M25" s="11">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
+        <v>119</v>
       </c>
       <c r="N25" s="11">
         <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="O25" s="6">
-        <v>46292</v>
+        <v>46272</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S25" s="5" t="s">
         <v>48</v>
@@ -10764,31 +10762,31 @@
         <v>0</v>
       </c>
       <c r="AC25" s="6">
-        <v>46220</v>
+        <v>46202</v>
       </c>
       <c r="AD25" s="7">
         <v>6392.96</v>
       </c>
       <c r="AE25" s="4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AF25" s="5" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="AG25" s="5" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="AL25" s="5" t="s">
         <v>64</v>
       </c>
       <c r="AM25" s="6">
-        <v>46204</v>
+        <v>46191</v>
       </c>
       <c r="AN25" s="5" t="s">
         <v>179</v>
@@ -10799,61 +10797,61 @@
         <v>67</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>527</v>
+        <v>216</v>
       </c>
       <c r="C26" s="3">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="D26" s="4">
-        <v>572251031</v>
+        <v>563172458</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="F26" s="6">
-        <v>46202</v>
+        <v>46191</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="K26" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
       <c r="L26" s="11">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>-8</v>
+        <v>-19</v>
       </c>
       <c r="M26" s="11">
-        <f ca="1">IF($F26="","",$F26+90-TODAY())</f>
-        <v>-8</v>
+        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <v>97</v>
       </c>
       <c r="N26" s="11">
         <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O26" s="6">
-        <v>46292</v>
+        <v>46281</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>49</v>
@@ -10862,15 +10860,15 @@
         <v>48</v>
       </c>
       <c r="V26" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Z26" s="7">
-        <v>36353.800000000003</v>
+        <v>2958.2</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -10880,10 +10878,10 @@
       </c>
       <c r="AC26" s="6"/>
       <c r="AD26" s="7">
-        <v>36353.800000000003</v>
+        <v>2958.2</v>
       </c>
       <c r="AE26" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AF26" s="5" t="s">
         <v>102</v>
@@ -10893,36 +10891,36 @@
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>245</v>
+        <v>64</v>
       </c>
       <c r="AM26" s="6">
-        <v>46205</v>
+        <v>46196</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="C27" s="15">
-        <v>46265</v>
+      <c r="B27" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46220</v>
       </c>
       <c r="D27" s="4">
-        <v>567785138</v>
+        <v>564043829</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="F27" s="6">
-        <v>46202</v>
+        <v>46196</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>70</v>
@@ -10934,25 +10932,25 @@
         <v>43</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="K27" s="3">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L27" s="11">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="M27" s="11">
         <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="N27" s="11">
         <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="O27" s="6">
-        <v>46292</v>
+        <v>46286</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>45</v>
@@ -10973,15 +10971,15 @@
         <v>48</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Z27" s="7">
-        <v>5916.4</v>
+        <v>9479.4</v>
       </c>
       <c r="AA27" s="7">
         <v>0</v>
@@ -10989,30 +10987,30 @@
       <c r="AB27" s="7">
         <v>0</v>
       </c>
-      <c r="AC27" s="6"/>
+      <c r="AC27" s="6">
+        <v>46220</v>
+      </c>
       <c r="AD27" s="7">
-        <v>5916.4</v>
+        <v>9479.4</v>
       </c>
       <c r="AE27" s="4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG27" s="5" t="s">
-        <v>249</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AM27" s="6">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="AN27" s="5" t="s">
         <v>179</v>
@@ -11020,114 +11018,114 @@
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>529</v>
+        <v>67</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="C28" s="3">
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="D28" s="4">
-        <v>563158507</v>
+        <v>564053524</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F28" s="6">
-        <v>46192</v>
+        <v>46202</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>252</v>
+        <v>70</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="K28" s="3">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L28" s="11">
         <f ca="1">IF($O28="","",$O28-TODAY())</f>
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="M28" s="11">
-        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
-        <v>84</v>
+        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <v>285</v>
       </c>
       <c r="N28" s="11">
-        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
-        <v>84</v>
+        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <v>285</v>
       </c>
       <c r="O28" s="6">
-        <v>46312</v>
+        <v>46292</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S28" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U28" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Z28" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AA28" s="7">
-        <v>945.04</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="7">
-        <v>3960.92</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="6">
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="AD28" s="7">
-        <v>1010.44</v>
+        <v>6392.96</v>
       </c>
       <c r="AE28" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF28" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG28" s="5"/>
+        <v>239</v>
+      </c>
+      <c r="AG28" s="5" t="s">
+        <v>240</v>
+      </c>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
-      <c r="AJ28" s="4">
-        <v>565293130</v>
-      </c>
+      <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="AL28" s="5" t="s">
         <v>64</v>
       </c>
       <c r="AM28" s="6">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="AN28" s="5" t="s">
         <v>179</v>
@@ -11135,64 +11133,64 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>180</v>
+        <v>67</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>527</v>
       </c>
       <c r="C29" s="3">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="D29" s="4">
-        <v>562162337</v>
+        <v>572251031</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="F29" s="6">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="K29" s="3">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="L29" s="11">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>-36</v>
+        <v>-8</v>
       </c>
       <c r="M29" s="11">
-        <f ca="1">IF($C29="","",$C29+180-TODAY())</f>
-        <v>92</v>
+        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
+        <v>-8</v>
       </c>
       <c r="N29" s="11">
         <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="O29" s="6">
-        <v>46264</v>
+        <v>46292</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>49</v>
@@ -11201,7 +11199,7 @@
         <v>48</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
@@ -11209,7 +11207,7 @@
         <v>175</v>
       </c>
       <c r="Z29" s="7">
-        <v>5916.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA29" s="7">
         <v>0</v>
@@ -11217,14 +11215,12 @@
       <c r="AB29" s="7">
         <v>0</v>
       </c>
-      <c r="AC29" s="6">
-        <v>46212</v>
-      </c>
+      <c r="AC29" s="6"/>
       <c r="AD29" s="7">
-        <v>5916.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE29" s="4">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>102</v>
@@ -11234,13 +11230,13 @@
       <c r="AI29" s="5"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5" t="s">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="AL29" s="5" t="s">
-        <v>64</v>
+        <v>245</v>
       </c>
       <c r="AM29" s="6">
-        <v>46185</v>
+        <v>46205</v>
       </c>
       <c r="AN29" s="5" t="s">
         <v>179</v>
@@ -11248,22 +11244,22 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="3">
-        <v>46224</v>
+        <v>528</v>
+      </c>
+      <c r="C30" s="15">
+        <v>46265</v>
       </c>
       <c r="D30" s="4">
-        <v>563985783</v>
+        <v>567785138</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>185</v>
+        <v>248</v>
       </c>
       <c r="F30" s="6">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>70</v>
@@ -11278,22 +11274,22 @@
         <v>182</v>
       </c>
       <c r="K30" s="3">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="L30" s="11">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>-36</v>
+        <v>-8</v>
       </c>
       <c r="M30" s="11">
         <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="N30" s="11">
         <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="O30" s="6">
-        <v>46264</v>
+        <v>46292</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>45</v>
@@ -11330,32 +11326,30 @@
       <c r="AB30" s="7">
         <v>0</v>
       </c>
-      <c r="AC30" s="6">
-        <v>46224</v>
-      </c>
+      <c r="AC30" s="6"/>
       <c r="AD30" s="7">
         <v>5916.4</v>
       </c>
       <c r="AE30" s="4">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AF30" s="5" t="s">
         <v>102</v>
       </c>
       <c r="AG30" s="5" t="s">
-        <v>186</v>
+        <v>249</v>
       </c>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5" t="s">
-        <v>187</v>
+        <v>250</v>
       </c>
       <c r="AL30" s="5" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="AM30" s="6">
-        <v>46185</v>
+        <v>46205</v>
       </c>
       <c r="AN30" s="5" t="s">
         <v>179</v>
@@ -11363,114 +11357,114 @@
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>188</v>
+        <v>529</v>
       </c>
       <c r="C31" s="3">
-        <v>46212</v>
+        <v>46204</v>
       </c>
       <c r="D31" s="4">
-        <v>562140119</v>
+        <v>563158507</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="F31" s="6">
-        <v>46175</v>
+        <v>46192</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>70</v>
+        <v>252</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="K31" s="3">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="L31" s="11">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
-        <v>-35</v>
+        <v>12</v>
       </c>
       <c r="M31" s="11">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>277</v>
+        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <v>84</v>
       </c>
       <c r="N31" s="11">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>277</v>
+        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
+        <v>84</v>
       </c>
       <c r="O31" s="6">
-        <v>46265</v>
+        <v>46312</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="R31" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S31" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T31" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U31" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="Z31" s="7">
-        <v>11832.8</v>
+        <v>5916.4</v>
       </c>
       <c r="AA31" s="7">
-        <v>0</v>
+        <v>945.04</v>
       </c>
       <c r="AB31" s="7">
-        <v>0</v>
+        <v>3960.92</v>
       </c>
       <c r="AC31" s="6">
-        <v>46212</v>
+        <v>46204</v>
       </c>
       <c r="AD31" s="7">
-        <v>11832.8</v>
+        <v>1010.44</v>
       </c>
       <c r="AE31" s="4">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AF31" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG31" s="5" t="s">
-        <v>193</v>
-      </c>
+      <c r="AG31" s="5"/>
       <c r="AH31" s="5"/>
       <c r="AI31" s="5"/>
-      <c r="AJ31" s="4"/>
+      <c r="AJ31" s="4">
+        <v>565293130</v>
+      </c>
       <c r="AK31" s="5" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AL31" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AM31" s="6">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="AN31" s="5" t="s">
         <v>179</v>
@@ -11478,64 +11472,64 @@
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>590</v>
+        <v>40</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="C32" s="3">
-        <v>46281</v>
+        <v>46212</v>
       </c>
       <c r="D32" s="4">
-        <v>562623275</v>
+        <v>562162337</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>536</v>
+        <v>181</v>
       </c>
       <c r="F32" s="6">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="K32" s="3">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="L32" s="11">
         <f ca="1">IF($O32="","",$O32-TODAY())</f>
-        <v>-29</v>
+        <v>-36</v>
       </c>
       <c r="M32" s="11">
-        <f ca="1">IF($F32="","",$F32+90-TODAY())</f>
-        <v>-29</v>
+        <f ca="1">IF($C32="","",$C32+180-TODAY())</f>
+        <v>92</v>
       </c>
       <c r="N32" s="11">
         <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="O32" s="6">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="P32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q32" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="R32" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>49</v>
@@ -11544,7 +11538,7 @@
         <v>48</v>
       </c>
       <c r="V32" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
@@ -11552,7 +11546,7 @@
         <v>175</v>
       </c>
       <c r="Z32" s="7">
-        <v>36353.800000000003</v>
+        <v>5916.4</v>
       </c>
       <c r="AA32" s="7">
         <v>0</v>
@@ -11560,12 +11554,14 @@
       <c r="AB32" s="7">
         <v>0</v>
       </c>
-      <c r="AC32" s="6"/>
+      <c r="AC32" s="6">
+        <v>46212</v>
+      </c>
       <c r="AD32" s="7">
-        <v>36353.800000000003</v>
+        <v>5916.4</v>
       </c>
       <c r="AE32" s="4">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF32" s="5" t="s">
         <v>102</v>
@@ -11581,7 +11577,7 @@
         <v>64</v>
       </c>
       <c r="AM32" s="6">
-        <v>46274</v>
+        <v>46185</v>
       </c>
       <c r="AN32" s="5" t="s">
         <v>179</v>
@@ -11592,58 +11588,58 @@
         <v>40</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="C33" s="3">
-        <v>46202</v>
+        <v>46224</v>
       </c>
       <c r="D33" s="4">
-        <v>562729752</v>
+        <v>563985783</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F33" s="6">
-        <v>46189</v>
+        <v>46174</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="K33" s="3">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="L33" s="11">
         <f ca="1">IF($O33="","",$O33-TODAY())</f>
-        <v>-21</v>
+        <v>-36</v>
       </c>
       <c r="M33" s="11">
-        <f ca="1">IF($C33="","",$C33+180-TODAY())</f>
-        <v>82</v>
+        <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
+        <v>289</v>
       </c>
       <c r="N33" s="11">
         <f ca="1">IF($C33="","",$C33+365-TODAY())</f>
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="O33" s="6">
-        <v>46279</v>
+        <v>46264</v>
       </c>
       <c r="P33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S33" s="5" t="s">
         <v>48</v>
@@ -11660,10 +11656,10 @@
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
       <c r="Y33" s="5" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="Z33" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA33" s="7">
         <v>0</v>
@@ -11672,29 +11668,31 @@
         <v>0</v>
       </c>
       <c r="AC33" s="6">
-        <v>46202</v>
+        <v>46224</v>
       </c>
       <c r="AD33" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE33" s="4">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AF33" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="AL33" s="5" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="AM33" s="6">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="AN33" s="5" t="s">
         <v>179</v>
@@ -11705,61 +11703,61 @@
         <v>40</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>533</v>
+        <v>188</v>
       </c>
       <c r="C34" s="3">
-        <v>46203</v>
+        <v>46212</v>
       </c>
       <c r="D34" s="4">
-        <v>571030818</v>
+        <v>562140119</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="F34" s="6">
-        <v>46191</v>
+        <v>46175</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="K34" s="3">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="L34" s="11">
         <f ca="1">IF($O34="","",$O34-TODAY())</f>
-        <v>-19</v>
+        <v>-35</v>
       </c>
       <c r="M34" s="11">
-        <f ca="1">IF($F34="","",$F34+90-TODAY())</f>
-        <v>-19</v>
+        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
+        <v>277</v>
       </c>
       <c r="N34" s="11">
         <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="O34" s="6">
-        <v>46281</v>
+        <v>46265</v>
       </c>
       <c r="P34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T34" s="5" t="s">
         <v>49</v>
@@ -11768,15 +11766,15 @@
         <v>48</v>
       </c>
       <c r="V34" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
       <c r="Y34" s="5" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="Z34" s="7">
-        <v>2958.2</v>
+        <v>11832.8</v>
       </c>
       <c r="AA34" s="7">
         <v>0</v>
@@ -11784,28 +11782,32 @@
       <c r="AB34" s="7">
         <v>0</v>
       </c>
-      <c r="AC34" s="6"/>
+      <c r="AC34" s="6">
+        <v>46212</v>
+      </c>
       <c r="AD34" s="7">
-        <v>2958.2</v>
+        <v>11832.8</v>
       </c>
       <c r="AE34" s="4">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="AF34" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5" t="s">
+        <v>193</v>
+      </c>
       <c r="AH34" s="5"/>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="AL34" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AM34" s="6">
-        <v>46196</v>
+        <v>46185</v>
       </c>
       <c r="AN34" s="5" t="s">
         <v>179</v>
@@ -11813,64 +11815,64 @@
     </row>
     <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>515</v>
+        <v>590</v>
       </c>
       <c r="C35" s="3">
-        <v>46204</v>
+        <v>46281</v>
       </c>
       <c r="D35" s="4">
-        <v>563159449</v>
+        <v>562623275</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>219</v>
+        <v>536</v>
       </c>
       <c r="F35" s="6">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="K35" s="3">
-        <v>46282</v>
+        <v>46274</v>
       </c>
       <c r="L35" s="11">
         <f ca="1">IF($O35="","",$O35-TODAY())</f>
-        <v>-15</v>
+        <v>-29</v>
       </c>
       <c r="M35" s="11">
-        <f ca="1">IF($C35="","",$C35+180-TODAY())</f>
-        <v>84</v>
+        <f ca="1">IF($F35="","",$F35+90-TODAY())</f>
+        <v>-29</v>
       </c>
       <c r="N35" s="11">
         <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="O35" s="6">
-        <v>46285</v>
+        <v>46271</v>
       </c>
       <c r="P35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R35" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T35" s="5" t="s">
         <v>49</v>
@@ -11879,7 +11881,7 @@
         <v>48</v>
       </c>
       <c r="V35" s="5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
@@ -11887,7 +11889,7 @@
         <v>175</v>
       </c>
       <c r="Z35" s="7">
-        <v>5916.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA35" s="7">
         <v>0</v>
@@ -11897,30 +11899,26 @@
       </c>
       <c r="AC35" s="6"/>
       <c r="AD35" s="7">
-        <v>5916.4</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE35" s="4">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="AF35" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG35" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="AH35" s="5" t="s">
-        <v>221</v>
-      </c>
+      <c r="AG35" s="5"/>
+      <c r="AH35" s="5"/>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="AL35" s="5" t="s">
         <v>64</v>
       </c>
       <c r="AM35" s="6">
-        <v>46196</v>
+        <v>46274</v>
       </c>
       <c r="AN35" s="5" t="s">
         <v>179</v>
@@ -11931,58 +11929,58 @@
         <v>40</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>516</v>
+        <v>207</v>
       </c>
       <c r="C36" s="3">
-        <v>46222</v>
+        <v>46202</v>
       </c>
       <c r="D36" s="4">
-        <v>563166125</v>
+        <v>562729752</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F36" s="6">
-        <v>46195</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>70</v>
+        <v>46189</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="K36" s="3">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="L36" s="11">
         <f ca="1">IF($O36="","",$O36-TODAY())</f>
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="M36" s="11">
-        <f ca="1">IF($C36="","",$C36+365-TODAY())</f>
-        <v>287</v>
+        <f ca="1">IF($C36="","",$C36+180-TODAY())</f>
+        <v>82</v>
       </c>
       <c r="N36" s="11">
         <f ca="1">IF($C36="","",$C36+365-TODAY())</f>
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="O36" s="6">
-        <v>46285</v>
+        <v>46279</v>
       </c>
       <c r="P36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S36" s="5" t="s">
         <v>48</v>
@@ -11999,10 +11997,10 @@
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Z36" s="7">
-        <v>5916.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AA36" s="7">
         <v>0</v>
@@ -12011,31 +12009,29 @@
         <v>0</v>
       </c>
       <c r="AC36" s="6">
-        <v>46222</v>
+        <v>46202</v>
       </c>
       <c r="AD36" s="7">
-        <v>5916.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AE36" s="4">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AF36" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG36" s="5" t="s">
-        <v>176</v>
-      </c>
+      <c r="AG36" s="5"/>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="AL36" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AM36" s="6">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="AN36" s="5" t="s">
         <v>179</v>
@@ -12046,19 +12042,19 @@
         <v>40</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="C37" s="3">
-        <v>46210</v>
+        <v>46203</v>
       </c>
       <c r="D37" s="4">
-        <v>563202959</v>
+        <v>571030818</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F37" s="6">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>98</v>
@@ -12067,28 +12063,28 @@
         <v>98</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="K37" s="3">
         <v>46282</v>
       </c>
       <c r="L37" s="11">
         <f ca="1">IF($O37="","",$O37-TODAY())</f>
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="M37" s="11">
         <f ca="1">IF($F37="","",$F37+90-TODAY())</f>
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="N37" s="11">
         <f ca="1">IF($C37="","",$C37+365-TODAY())</f>
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="O37" s="6">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="P37" s="5" t="s">
         <v>45</v>
@@ -12109,15 +12105,15 @@
         <v>48</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="Z37" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AA37" s="7">
         <v>0</v>
@@ -12125,24 +12121,22 @@
       <c r="AB37" s="7">
         <v>0</v>
       </c>
-      <c r="AC37" s="6">
-        <v>46210</v>
-      </c>
+      <c r="AC37" s="6"/>
       <c r="AD37" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AE37" s="4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AF37" s="5" t="s">
-        <v>229</v>
+        <v>102</v>
       </c>
       <c r="AG37" s="5"/>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="AL37" s="5" t="s">
         <v>64</v>
@@ -12159,61 +12153,61 @@
         <v>40</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C38" s="3">
-        <v>46243</v>
+        <v>46204</v>
       </c>
       <c r="D38" s="4">
-        <v>564106567</v>
+        <v>563159449</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="F38" s="6">
-        <v>46198</v>
+        <v>46195</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="K38" s="3">
-        <v>46243</v>
+        <v>46282</v>
       </c>
       <c r="L38" s="11">
         <f ca="1">IF($O38="","",$O38-TODAY())</f>
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="M38" s="11">
-        <f ca="1">IF($F38="","",$F38+90-TODAY())</f>
-        <v>-12</v>
+        <f ca="1">IF($C38="","",$C38+180-TODAY())</f>
+        <v>84</v>
       </c>
       <c r="N38" s="11">
         <f ca="1">IF($C38="","",$C38+365-TODAY())</f>
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="O38" s="6">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="P38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="R38" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T38" s="5" t="s">
         <v>49</v>
@@ -12227,10 +12221,10 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="Z38" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA38" s="7">
         <v>0</v>
@@ -12240,28 +12234,30 @@
       </c>
       <c r="AC38" s="6"/>
       <c r="AD38" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE38" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF38" s="5" t="s">
         <v>102</v>
       </c>
       <c r="AG38" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="AH38" s="5"/>
+        <v>220</v>
+      </c>
+      <c r="AH38" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="AI38" s="5"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5" t="s">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AL38" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AM38" s="6">
-        <v>46205</v>
+        <v>46196</v>
       </c>
       <c r="AN38" s="5" t="s">
         <v>179</v>
@@ -12272,58 +12268,58 @@
         <v>40</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C39" s="3">
-        <v>46210</v>
+        <v>46222</v>
       </c>
       <c r="D39" s="4">
-        <v>564118055</v>
+        <v>563166125</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="F39" s="6">
-        <v>46202</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>93</v>
+        <v>46195</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="K39" s="3">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L39" s="11">
         <f ca="1">IF($O39="","",$O39-TODAY())</f>
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="M39" s="11">
-        <f ca="1">IF($C39="","",$C39+180-TODAY())</f>
-        <v>90</v>
+        <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
+        <v>287</v>
       </c>
       <c r="N39" s="11">
         <f ca="1">IF($C39="","",$C39+365-TODAY())</f>
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="O39" s="6">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="P39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="R39" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S39" s="5" t="s">
         <v>48</v>
@@ -12340,10 +12336,10 @@
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="Z39" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA39" s="7">
         <v>0</v>
@@ -12351,28 +12347,32 @@
       <c r="AB39" s="7">
         <v>0</v>
       </c>
-      <c r="AC39" s="6"/>
+      <c r="AC39" s="6">
+        <v>46222</v>
+      </c>
       <c r="AD39" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE39" s="4">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AF39" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="AH39" s="5"/>
       <c r="AI39" s="5"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="AL39" s="5" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="AM39" s="6">
-        <v>46205</v>
+        <v>46196</v>
       </c>
       <c r="AN39" s="5" t="s">
         <v>179</v>
@@ -12382,62 +12382,62 @@
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C40" s="15">
-        <v>46289</v>
+      <c r="B40" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46210</v>
       </c>
       <c r="D40" s="4">
-        <v>572251311</v>
+        <v>563202959</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="F40" s="6">
-        <v>46202</v>
+        <v>46195</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>247</v>
+        <v>98</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>247</v>
+        <v>98</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="K40" s="3">
-        <v>46300</v>
+        <v>46282</v>
       </c>
       <c r="L40" s="11">
         <f ca="1">IF($O40="","",$O40-TODAY())</f>
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="M40" s="11">
-        <f ca="1">IF($C40="","",$C40+180-TODAY())</f>
-        <v>169</v>
+        <f ca="1">IF($F40="","",$F40+90-TODAY())</f>
+        <v>-15</v>
       </c>
       <c r="N40" s="11">
         <f ca="1">IF($C40="","",$C40+365-TODAY())</f>
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="O40" s="6">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="P40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T40" s="5" t="s">
         <v>49</v>
@@ -12446,15 +12446,15 @@
         <v>48</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
       <c r="Y40" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Z40" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AA40" s="7">
         <v>0</v>
@@ -12462,28 +12462,30 @@
       <c r="AB40" s="7">
         <v>0</v>
       </c>
-      <c r="AC40" s="6"/>
+      <c r="AC40" s="6">
+        <v>46210</v>
+      </c>
       <c r="AD40" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AE40" s="4">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AF40" s="5" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="AG40" s="5"/>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5" t="s">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="AL40" s="5" t="s">
         <v>64</v>
       </c>
       <c r="AM40" s="6">
-        <v>46217</v>
+        <v>46196</v>
       </c>
       <c r="AN40" s="5" t="s">
         <v>179</v>
@@ -12493,108 +12495,110 @@
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="13" t="s">
+        <v>517</v>
+      </c>
       <c r="C41" s="3">
-        <v>46217</v>
+        <v>46243</v>
       </c>
       <c r="D41" s="4">
-        <v>562140958</v>
+        <v>564106567</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="F41" s="6">
-        <v>46178</v>
+        <v>46198</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="K41" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="K41" s="3">
+        <v>46243</v>
+      </c>
       <c r="L41" s="11">
         <f ca="1">IF($O41="","",$O41-TODAY())</f>
-        <v>243</v>
+        <v>-12</v>
       </c>
       <c r="M41" s="11">
+        <f ca="1">IF($F41="","",$F41+90-TODAY())</f>
+        <v>-12</v>
+      </c>
+      <c r="N41" s="11">
         <f ca="1">IF($C41="","",$C41+365-TODAY())</f>
-        <v>282</v>
-      </c>
-      <c r="N41" s="11">
-        <f ca="1">IF($C41="","",$C41+120-TODAY())</f>
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="O41" s="6">
-        <v>46543</v>
+        <v>46288</v>
       </c>
       <c r="P41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="T41" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="Q41" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="R41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S41" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T41" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="U41" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Z41" s="7">
-        <v>36353.800000000003</v>
+        <v>2958.2</v>
       </c>
       <c r="AA41" s="7">
-        <v>31016.19</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="7">
-        <v>4252.7299999999996</v>
-      </c>
-      <c r="AC41" s="6">
-        <v>46217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC41" s="6"/>
       <c r="AD41" s="7">
-        <v>1084.8800000000001</v>
+        <v>2958.2</v>
       </c>
       <c r="AE41" s="4">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AF41" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG41" s="5"/>
+      <c r="AG41" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
-      <c r="AJ41" s="4">
-        <v>564721141</v>
-      </c>
+      <c r="AJ41" s="4"/>
       <c r="AK41" s="5" t="s">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AL41" s="5" t="s">
-        <v>278</v>
+        <v>54</v>
       </c>
       <c r="AM41" s="6">
-        <v>46185</v>
+        <v>46205</v>
       </c>
       <c r="AN41" s="5" t="s">
         <v>179</v>
@@ -12604,112 +12608,108 @@
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42" s="13" t="s">
+        <v>515</v>
+      </c>
       <c r="C42" s="3">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="D42" s="4">
-        <v>563164453</v>
+        <v>564118055</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="F42" s="6">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="K42" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="K42" s="3">
+        <v>46283</v>
+      </c>
       <c r="L42" s="11">
         <f ca="1">IF($O42="","",$O42-TODAY())</f>
-        <v>260</v>
+        <v>-8</v>
       </c>
       <c r="M42" s="11">
+        <f ca="1">IF($C42="","",$C42+180-TODAY())</f>
+        <v>90</v>
+      </c>
+      <c r="N42" s="11">
         <f ca="1">IF($C42="","",$C42+365-TODAY())</f>
-        <v>276</v>
-      </c>
-      <c r="N42" s="11">
-        <f ca="1">IF($C42="","",$C42+120-TODAY())</f>
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="O42" s="6">
-        <v>46560</v>
+        <v>46292</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q42" s="5" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="R42" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S42" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T42" s="5" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="U42" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V42" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
       <c r="Y42" s="5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Z42" s="7">
-        <v>36353.800000000003</v>
+        <v>2958.2</v>
       </c>
       <c r="AA42" s="7">
-        <v>31016.19</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="7">
-        <v>4252.7299999999996</v>
-      </c>
-      <c r="AC42" s="6">
-        <v>46211</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="6"/>
       <c r="AD42" s="7">
-        <v>1084.8800000000001</v>
+        <v>2958.2</v>
       </c>
       <c r="AE42" s="4">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AF42" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AG42" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="AH42" s="5" t="s">
-        <v>237</v>
-      </c>
+      <c r="AG42" s="5"/>
+      <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
-      <c r="AJ42" s="4">
-        <v>566076337</v>
-      </c>
+      <c r="AJ42" s="4"/>
       <c r="AK42" s="5" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="AL42" s="5" t="s">
-        <v>271</v>
+        <v>206</v>
       </c>
       <c r="AM42" s="6">
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="AN42" s="5" t="s">
         <v>179</v>
@@ -12719,87 +12719,89 @@
       <c r="A43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="3">
-        <v>46219</v>
+      <c r="B43" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C43" s="15">
+        <v>46289</v>
       </c>
       <c r="D43" s="4">
-        <v>564117213</v>
+        <v>572251311</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="F43" s="6">
         <v>46202</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>295</v>
+        <v>43</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="K43" s="3"/>
+        <v>182</v>
+      </c>
+      <c r="K43" s="3">
+        <v>46300</v>
+      </c>
       <c r="L43" s="11">
         <f ca="1">IF($O43="","",$O43-TODAY())</f>
-        <v>267</v>
+        <v>-8</v>
       </c>
       <c r="M43" s="11">
+        <f ca="1">IF($C43="","",$C43+180-TODAY())</f>
+        <v>169</v>
+      </c>
+      <c r="N43" s="11">
         <f ca="1">IF($C43="","",$C43+365-TODAY())</f>
-        <v>284</v>
-      </c>
-      <c r="N43" s="11">
-        <f ca="1">IF($C43="","",$C43+120-TODAY())</f>
-        <v>39</v>
+        <v>354</v>
       </c>
       <c r="O43" s="6">
-        <v>46567</v>
+        <v>46292</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S43" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T43" s="5" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="U43" s="5" t="s">
         <v>48</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
       <c r="Y43" s="5" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="Z43" s="7">
-        <v>11832.8</v>
+        <v>5916.4</v>
       </c>
       <c r="AA43" s="7">
-        <v>10095.450000000001</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="7">
-        <v>1384.23</v>
-      </c>
-      <c r="AC43" s="6">
-        <v>46219</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC43" s="6"/>
       <c r="AD43" s="7">
-        <v>353.12</v>
+        <v>5916.4</v>
       </c>
       <c r="AE43" s="4">
         <v>40</v>
@@ -12810,17 +12812,15 @@
       <c r="AG43" s="5"/>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
-      <c r="AJ43" s="4">
-        <v>567247169</v>
-      </c>
+      <c r="AJ43" s="4"/>
       <c r="AK43" s="5" t="s">
-        <v>264</v>
+        <v>203</v>
       </c>
       <c r="AL43" s="5" t="s">
-        <v>265</v>
+        <v>64</v>
       </c>
       <c r="AM43" s="6">
-        <v>46205</v>
+        <v>46217</v>
       </c>
       <c r="AN43" s="5" t="s">
         <v>179</v>

--- a/SPC26S1 - 06 June.xlsx
+++ b/SPC26S1 - 06 June.xlsx
@@ -2507,7 +2507,7 @@
     <t>Past due rows sit below the claims that can still be filed on time rather than at the very top, so the actionable work stays first. That is why the numbers run up to the longest window and then restart at the negatives.</t>
   </si>
   <si>
-    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the three groups above back together, so when you re-sort keep the empty Latest Date Worked rows first and the Finalized and PAID rows last.</t>
+    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the four groups above back together, so when you re-sort keep the Rejected rows first, then the empty Latest Date Worked rows, and the Finalized and PAID rows last.</t>
   </si>
   <si>
     <t>Where a payer had two possible limits the shorter one was used, so the real deadline can only be later, never earlier. Filing Limit and Limit Carrier name the figure applied and the carrier row it came from.</t>
@@ -2735,7 +2735,7 @@
     <t>136 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -4459,56 +4459,56 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46240</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="4">
-        <v>562510277</v>
+        <v>562674720</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="F2" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="K2" s="3">
+        <v>46300</v>
+      </c>
       <c r="L2" s="11">
         <f ca="1">IF($O2="","",$O2-TODAY())</f>
-        <v>-21</v>
-      </c>
-      <c r="M2" s="11">
+        <v>10</v>
+      </c>
+      <c r="M2" s="11" t="str">
         <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
-        <v>120</v>
-      </c>
-      <c r="N2" s="11">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>305</v>
+        <v/>
+      </c>
+      <c r="N2" s="11" t="str">
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <v/>
       </c>
       <c r="O2" s="6">
-        <v>46279</v>
+        <v>46310</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>47</v>
@@ -4517,7 +4517,7 @@
         <v>48</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>48</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="Z2" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -4539,28 +4539,26 @@
       </c>
       <c r="AC2" s="6"/>
       <c r="AD2" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AE2" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG2" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="AM2" s="6">
-        <v>46233</v>
+        <v>46217</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>55</v>
@@ -4568,57 +4566,59 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>564</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>585</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>565</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46240</v>
+      </c>
       <c r="D3" s="4">
-        <v>563029504</v>
+        <v>562510277</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="F3" s="6">
-        <v>46195</v>
+        <v>46189</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="11">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>-15</v>
-      </c>
-      <c r="M3" s="11" t="str">
+        <v>-21</v>
+      </c>
+      <c r="M3" s="11">
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v>120</v>
+      </c>
+      <c r="N3" s="11">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N3" s="11" t="str">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v/>
+        <v>305</v>
       </c>
       <c r="O3" s="6">
-        <v>46285</v>
+        <v>46279</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>48</v>
@@ -4636,7 +4636,7 @@
         <v>50</v>
       </c>
       <c r="Z3" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -4646,54 +4646,58 @@
       </c>
       <c r="AC3" s="6"/>
       <c r="AD3" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AE3" s="4">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG3" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AM3" s="6">
-        <v>46273</v>
+        <v>46233</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3">
-        <v>46225</v>
-      </c>
+      <c r="A4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="4">
-        <v>561218278</v>
+        <v>563029504</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>122</v>
+        <v>548</v>
       </c>
       <c r="F4" s="6">
-        <v>46175</v>
+        <v>46195</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>56</v>
@@ -4701,24 +4705,24 @@
       <c r="K4" s="3"/>
       <c r="L4" s="11">
         <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v>240</v>
-      </c>
-      <c r="M4" s="11">
+        <v>-15</v>
+      </c>
+      <c r="M4" s="11" t="str">
         <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>290</v>
-      </c>
-      <c r="N4" s="11">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N4" s="11" t="str">
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O4" s="6">
+        <v>46285</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="6">
-        <v>46540</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="Q4" s="5" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>49</v>
@@ -4727,7 +4731,7 @@
         <v>48</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>48</v>
@@ -4747,14 +4751,12 @@
       <c r="AB4" s="7">
         <v>0</v>
       </c>
-      <c r="AC4" s="6">
-        <v>46225</v>
-      </c>
+      <c r="AC4" s="6"/>
       <c r="AD4" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE4" s="4">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AF4" s="5" t="s">
         <v>63</v>
@@ -4764,13 +4766,13 @@
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AM4" s="6">
-        <v>46217</v>
+        <v>46273</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>55</v>
@@ -4778,16 +4780,18 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3">
+        <v>46225</v>
+      </c>
       <c r="D5" s="4">
-        <v>561646597</v>
+        <v>561218278</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>554</v>
+        <v>122</v>
       </c>
       <c r="F5" s="6">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>120</v>
@@ -4796,26 +4800,26 @@
         <v>120</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="11">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>243</v>
-      </c>
-      <c r="M5" s="11" t="str">
+        <v>240</v>
+      </c>
+      <c r="M5" s="11">
         <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N5" s="11" t="str">
+        <v>290</v>
+      </c>
+      <c r="N5" s="11">
         <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="O5" s="6">
-        <v>46543</v>
+        <v>46540</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>49</v>
@@ -4842,7 +4846,7 @@
         <v>50</v>
       </c>
       <c r="Z5" s="7">
-        <v>1029.98</v>
+        <v>1426.25</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -4850,28 +4854,30 @@
       <c r="AB5" s="7">
         <v>0</v>
       </c>
-      <c r="AC5" s="6"/>
+      <c r="AC5" s="6">
+        <v>46225</v>
+      </c>
       <c r="AD5" s="7">
-        <v>1029.98</v>
+        <v>1426.25</v>
       </c>
       <c r="AE5" s="4">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>555</v>
+        <v>63</v>
       </c>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AM5" s="6">
-        <v>46274</v>
+        <v>46217</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>55</v>
@@ -4879,18 +4885,16 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3">
-        <v>46226</v>
-      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="4">
-        <v>561886342</v>
+        <v>561646597</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>128</v>
+        <v>554</v>
       </c>
       <c r="F6" s="6">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>120</v>
@@ -4899,26 +4903,26 @@
         <v>120</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="11">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>247</v>
-      </c>
-      <c r="M6" s="11">
+        <v>243</v>
+      </c>
+      <c r="M6" s="11" t="str">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>291</v>
-      </c>
-      <c r="N6" s="11">
+        <v/>
+      </c>
+      <c r="N6" s="11" t="str">
         <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
-        <v>46</v>
+        <v/>
       </c>
       <c r="O6" s="6">
-        <v>46547</v>
+        <v>46543</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>49</v>
@@ -4945,7 +4949,7 @@
         <v>50</v>
       </c>
       <c r="Z6" s="7">
-        <v>1426.25</v>
+        <v>1029.98</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -4953,30 +4957,28 @@
       <c r="AB6" s="7">
         <v>0</v>
       </c>
-      <c r="AC6" s="6">
-        <v>46226</v>
-      </c>
+      <c r="AC6" s="6"/>
       <c r="AD6" s="7">
-        <v>1426.25</v>
+        <v>1029.98</v>
       </c>
       <c r="AE6" s="4">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>63</v>
+        <v>555</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AM6" s="6">
-        <v>46217</v>
+        <v>46274</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>55</v>
@@ -4989,13 +4991,13 @@
         <v>46226</v>
       </c>
       <c r="D7" s="4">
-        <v>561898000</v>
+        <v>561886342</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F7" s="6">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>120</v>
@@ -5004,15 +5006,15 @@
         <v>120</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="11">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M7" s="11">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
@@ -5023,7 +5025,7 @@
         <v>46</v>
       </c>
       <c r="O7" s="6">
-        <v>46548</v>
+        <v>46547</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>49</v>
@@ -5050,7 +5052,7 @@
         <v>50</v>
       </c>
       <c r="Z7" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -5062,23 +5064,23 @@
         <v>46226</v>
       </c>
       <c r="AD7" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE7" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AM7" s="6">
         <v>46217</v>
@@ -5091,16 +5093,16 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D8" s="4">
-        <v>562843131</v>
+        <v>561898000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F8" s="6">
-        <v>46192</v>
+        <v>46183</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>120</v>
@@ -5109,7 +5111,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>81</v>
@@ -5117,18 +5119,18 @@
       <c r="K8" s="3"/>
       <c r="L8" s="11">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M8" s="11">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N8" s="11">
         <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O8" s="6">
-        <v>46557</v>
+        <v>46548</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>49</v>
@@ -5164,23 +5166,23 @@
         <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="AD8" s="7">
         <v>1372.91</v>
       </c>
       <c r="AE8" s="4">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="AL8" s="5" t="s">
         <v>59</v>
@@ -5195,15 +5197,17 @@
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>46225</v>
+      </c>
       <c r="D9" s="4">
-        <v>563651212</v>
+        <v>562843131</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F9" s="6">
-        <v>46199</v>
+        <v>46192</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>120</v>
@@ -5212,7 +5216,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>81</v>
@@ -5220,18 +5224,18 @@
       <c r="K9" s="3"/>
       <c r="L9" s="11">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>264</v>
-      </c>
-      <c r="M9" s="11" t="str">
+        <v>257</v>
+      </c>
+      <c r="M9" s="11">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N9" s="11" t="str">
+        <v>290</v>
+      </c>
+      <c r="N9" s="11">
         <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="O9" s="6">
-        <v>46564</v>
+        <v>46557</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>49</v>
@@ -5266,25 +5270,27 @@
       <c r="AB9" s="7">
         <v>0</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="6">
+        <v>46225</v>
+      </c>
       <c r="AD9" s="7">
         <v>1372.91</v>
       </c>
       <c r="AE9" s="4">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AM9" s="6">
         <v>46217</v>
@@ -5296,17 +5302,15 @@
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="3">
-        <v>46225</v>
-      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="4">
-        <v>563782794</v>
+        <v>563651212</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F10" s="6">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>120</v>
@@ -5315,26 +5319,26 @@
         <v>120</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="11">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>267</v>
-      </c>
-      <c r="M10" s="11">
+        <v>264</v>
+      </c>
+      <c r="M10" s="11" t="str">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>290</v>
-      </c>
-      <c r="N10" s="11">
+        <v/>
+      </c>
+      <c r="N10" s="11" t="str">
         <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="O10" s="6">
-        <v>46567</v>
+        <v>46564</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>49</v>
@@ -5361,7 +5365,7 @@
         <v>50</v>
       </c>
       <c r="Z10" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -5369,27 +5373,25 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6">
-        <v>46225</v>
-      </c>
+      <c r="AC10" s="6"/>
       <c r="AD10" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE10" s="4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AM10" s="6">
         <v>46217</v>
@@ -5400,16 +5402,18 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3">
+        <v>46225</v>
+      </c>
       <c r="D11" s="4">
-        <v>563850884</v>
+        <v>563782794</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>556</v>
+        <v>137</v>
       </c>
       <c r="F11" s="6">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>120</v>
@@ -5418,26 +5422,26 @@
         <v>120</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="11">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>268</v>
-      </c>
-      <c r="M11" s="11" t="str">
+        <v>267</v>
+      </c>
+      <c r="M11" s="11">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N11" s="11" t="str">
+        <v>290</v>
+      </c>
+      <c r="N11" s="11">
         <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="O11" s="6">
-        <v>46568</v>
+        <v>46567</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>49</v>
@@ -5464,7 +5468,7 @@
         <v>50</v>
       </c>
       <c r="Z11" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -5472,30 +5476,30 @@
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6"/>
+      <c r="AC11" s="6">
+        <v>46225</v>
+      </c>
       <c r="AD11" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AE11" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="AM11" s="6">
-        <v>46268</v>
+        <v>46217</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>55</v>
@@ -5503,48 +5507,64 @@
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4">
-        <v>561024208</v>
+        <v>563850884</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>141</v>
+        <v>556</v>
       </c>
       <c r="F12" s="6">
-        <v>46175</v>
+        <v>46203</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="11" t="str">
+      <c r="L12" s="11">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>268</v>
+      </c>
+      <c r="M12" s="11" t="str">
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="5"/>
+      <c r="N12" s="11" t="str">
+        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O12" s="6">
+        <v>46568</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="Q12" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5" t="s">
-        <v>145</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="V12" s="5"/>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
@@ -5564,29 +5584,25 @@
         <v>294.42</v>
       </c>
       <c r="AE12" s="4">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH12" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI12" s="5" t="s">
-        <v>149</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="AM12" s="6">
-        <v>46191</v>
+        <v>46268</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>55</v>
@@ -5595,29 +5611,27 @@
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="3">
-        <v>46218</v>
-      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="4">
-        <v>561219063</v>
+        <v>561024208</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F13" s="6">
         <v>46175</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="11" t="str">
@@ -5635,14 +5649,16 @@
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
+      <c r="V13" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z13" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -5650,30 +5666,34 @@
       <c r="AB13" s="7">
         <v>0</v>
       </c>
-      <c r="AC13" s="6">
-        <v>46218</v>
-      </c>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AE13" s="4">
         <v>67</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG13" s="5"/>
-      <c r="AH13" s="5"/>
-      <c r="AI13" s="5"/>
+        <v>146</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI13" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
         <v>74</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AM13" s="6">
-        <v>46217</v>
+        <v>46191</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>55</v>
@@ -5682,27 +5702,29 @@
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3">
+        <v>46218</v>
+      </c>
       <c r="D14" s="4">
-        <v>562198116</v>
+        <v>561219063</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F14" s="6">
-        <v>46185</v>
+        <v>46175</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="11" t="str">
@@ -5735,12 +5757,14 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="6">
+        <v>46218</v>
+      </c>
       <c r="AD14" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE14" s="4">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="AF14" s="5" t="s">
         <v>63</v>
@@ -5750,10 +5774,10 @@
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AM14" s="6">
         <v>46217</v>
@@ -5763,27 +5787,23 @@
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>566</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4">
-        <v>562518339</v>
+        <v>562198116</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F15" s="6">
-        <v>46189</v>
+        <v>46185</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>43</v>
@@ -5827,7 +5847,7 @@
         <v>1426.25</v>
       </c>
       <c r="AE15" s="4">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AF15" s="5" t="s">
         <v>63</v>
@@ -5837,10 +5857,10 @@
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="AM15" s="6">
         <v>46217</v>
@@ -5850,23 +5870,27 @@
       </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>566</v>
+      </c>
       <c r="C16" s="3"/>
       <c r="D16" s="4">
-        <v>562594958</v>
+        <v>562518339</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F16" s="6">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>43</v>
@@ -5910,20 +5934,20 @@
         <v>1426.25</v>
       </c>
       <c r="AE16" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AM16" s="6">
         <v>46217</v>
@@ -5937,25 +5961,25 @@
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4">
-        <v>562862986</v>
+        <v>562594958</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F17" s="6">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="11" t="str">
@@ -5963,23 +5987,16 @@
         <v/>
       </c>
       <c r="M17" s="11"/>
-      <c r="N17" s="11" t="str">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v/>
-      </c>
+      <c r="N17" s="11"/>
       <c r="O17" s="6"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
@@ -5987,7 +6004,7 @@
         <v>50</v>
       </c>
       <c r="Z17" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AA17" s="7">
         <v>0</v>
@@ -5997,28 +6014,26 @@
       </c>
       <c r="AC17" s="6"/>
       <c r="AD17" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AE17" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG17" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="AM17" s="6">
-        <v>46234</v>
+        <v>46217</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>55</v>
@@ -6029,25 +6044,25 @@
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4">
-        <v>562903580</v>
+        <v>562862986</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F18" s="6">
         <v>46192</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="11" t="str">
@@ -6055,16 +6070,23 @@
         <v/>
       </c>
       <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+      <c r="N18" s="11" t="str">
+        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <v/>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
+      <c r="T18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
@@ -6072,7 +6094,7 @@
         <v>50</v>
       </c>
       <c r="Z18" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -6082,26 +6104,28 @@
       </c>
       <c r="AC18" s="6"/>
       <c r="AD18" s="7">
-        <v>1426.25</v>
+        <v>294.42</v>
       </c>
       <c r="AE18" s="4">
         <v>50</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG18" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="AG18" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AM18" s="6">
-        <v>46217</v>
+        <v>46234</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>55</v>
@@ -6112,13 +6136,13 @@
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4">
-        <v>563421228</v>
+        <v>562903580</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F19" s="6">
-        <v>46198</v>
+        <v>46192</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>165</v>
@@ -6130,7 +6154,7 @@
         <v>43</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="11" t="str">
@@ -6168,7 +6192,7 @@
         <v>1426.25</v>
       </c>
       <c r="AE19" s="4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF19" s="5" t="s">
         <v>63</v>
@@ -6178,10 +6202,10 @@
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AM19" s="6">
         <v>46217</v>
@@ -6195,33 +6219,33 @@
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4">
-        <v>563470580</v>
+        <v>563421228</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F20" s="6">
         <v>46198</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="4" t="str">
+      <c r="L20" s="11" t="str">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
         <v/>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
       <c r="O20" s="6"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5" t="s">
@@ -6238,7 +6262,7 @@
         <v>50</v>
       </c>
       <c r="Z20" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AA20" s="7">
         <v>0</v>
@@ -6248,100 +6272,72 @@
       </c>
       <c r="AC20" s="6"/>
       <c r="AD20" s="7">
-        <v>294.42</v>
+        <v>1426.25</v>
       </c>
       <c r="AE20" s="4">
         <v>44</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AM20" s="6">
-        <v>46234</v>
+        <v>46217</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>588</v>
-      </c>
-      <c r="C21" s="3">
-        <v>46225</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="4">
-        <v>561646092</v>
+        <v>563470580</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>541</v>
+        <v>167</v>
       </c>
       <c r="F21" s="6">
-        <v>46177</v>
+        <v>46198</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>339</v>
+        <v>168</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K21" s="3">
-        <v>46248</v>
-      </c>
-      <c r="L21" s="11">
+        <v>85</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="4" t="str">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-33</v>
-      </c>
-      <c r="M21" s="11">
-        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
-        <v>-33</v>
-      </c>
-      <c r="N21" s="11">
-        <f ca="1">IF($C21="","",$C21+540-TODAY())</f>
-        <v>465</v>
-      </c>
-      <c r="O21" s="6">
-        <v>46267</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="5"/>
       <c r="Q21" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="T21" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
@@ -6349,42 +6345,38 @@
         <v>50</v>
       </c>
       <c r="Z21" s="7">
-        <v>1029.98</v>
+        <v>294.42</v>
       </c>
       <c r="AA21" s="7">
-        <v>883.53</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="7">
-        <v>121.45</v>
-      </c>
-      <c r="AC21" s="6">
-        <v>46225</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="6"/>
       <c r="AD21" s="7">
-        <v>25</v>
+        <v>294.42</v>
       </c>
       <c r="AE21" s="4">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
-      <c r="AJ21" s="4" t="s">
-        <v>543</v>
-      </c>
+      <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="AM21" s="6">
-        <v>46217</v>
+        <v>46234</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>55</v>
@@ -6392,67 +6384,67 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>68</v>
+        <v>588</v>
       </c>
       <c r="C22" s="3">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="D22" s="4">
-        <v>570976486</v>
+        <v>561646092</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>69</v>
+        <v>541</v>
       </c>
       <c r="F22" s="6">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>70</v>
+        <v>339</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="K22" s="3">
-        <v>46270</v>
+        <v>46248</v>
       </c>
       <c r="L22" s="11">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-28</v>
+        <v>-33</v>
       </c>
       <c r="M22" s="11">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>296</v>
+        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <v>-33</v>
       </c>
       <c r="N22" s="11">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>296</v>
+        <f ca="1">IF($C22="","",$C22+540-TODAY())</f>
+        <v>465</v>
       </c>
       <c r="O22" s="6">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>72</v>
+        <v>341</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>49</v>
+        <v>542</v>
       </c>
       <c r="U22" s="5" t="s">
         <v>48</v>
@@ -6464,33 +6456,39 @@
         <v>50</v>
       </c>
       <c r="Z22" s="7">
-        <v>1372.91</v>
+        <v>1029.98</v>
       </c>
       <c r="AA22" s="7">
-        <v>0</v>
+        <v>883.53</v>
       </c>
       <c r="AB22" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="6"/>
+        <v>121.45</v>
+      </c>
+      <c r="AC22" s="6">
+        <v>46225</v>
+      </c>
       <c r="AD22" s="7">
-        <v>1372.91</v>
+        <v>25</v>
       </c>
       <c r="AE22" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG22" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="AG22" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="4"/>
+      <c r="AJ22" s="4" t="s">
+        <v>543</v>
+      </c>
       <c r="AK22" s="5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AM22" s="6">
         <v>46217</v>
@@ -6504,25 +6502,25 @@
         <v>67</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C23" s="3">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="D23" s="4">
-        <v>571031540</v>
+        <v>570976486</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F23" s="6">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>43</v>
@@ -6531,31 +6529,31 @@
         <v>71</v>
       </c>
       <c r="K23" s="3">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="L23" s="11">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="M23" s="11">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>100</v>
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>296</v>
       </c>
       <c r="N23" s="11">
         <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="O23" s="6">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S23" s="5" t="s">
         <v>48</v>
@@ -6581,27 +6579,25 @@
       <c r="AB23" s="7">
         <v>0</v>
       </c>
-      <c r="AC23" s="6">
-        <v>46224</v>
-      </c>
+      <c r="AC23" s="6"/>
       <c r="AD23" s="7">
         <v>1372.91</v>
       </c>
       <c r="AE23" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AG23" s="5"/>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AM23" s="6">
         <v>46217</v>
@@ -6612,56 +6608,58 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>586</v>
-      </c>
-      <c r="C24" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46220</v>
+      </c>
       <c r="D24" s="4">
-        <v>562534504</v>
+        <v>571031540</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>547</v>
+        <v>77</v>
       </c>
       <c r="F24" s="6">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="K24" s="3">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="L24" s="11">
         <f ca="1">IF($O24="","",$O24-TODAY())</f>
-        <v>-21</v>
-      </c>
-      <c r="M24" s="11" t="str">
+        <v>-27</v>
+      </c>
+      <c r="M24" s="11">
         <f ca="1">IF($C24="","",$C24+180-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N24" s="11" t="str">
+        <v>100</v>
+      </c>
+      <c r="N24" s="11">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v/>
+        <v>285</v>
       </c>
       <c r="O24" s="6">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="R24" s="5" t="s">
         <v>47</v>
@@ -6682,7 +6680,7 @@
         <v>50</v>
       </c>
       <c r="Z24" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA24" s="7">
         <v>0</v>
@@ -6690,28 +6688,30 @@
       <c r="AB24" s="7">
         <v>0</v>
       </c>
-      <c r="AC24" s="6"/>
+      <c r="AC24" s="6">
+        <v>46224</v>
+      </c>
       <c r="AD24" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE24" s="4">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AF24" s="5" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="AL24" s="5" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="AM24" s="6">
-        <v>46274</v>
+        <v>46217</v>
       </c>
       <c r="AN24" s="5" t="s">
         <v>55</v>
@@ -6721,37 +6721,37 @@
       <c r="A25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>91</v>
+      <c r="B25" s="13" t="s">
+        <v>586</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="4">
-        <v>562803289</v>
+        <v>562534504</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>92</v>
+        <v>547</v>
       </c>
       <c r="F25" s="6">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="K25" s="3">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="L25" s="11">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="M25" s="11" t="str">
         <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
@@ -6762,13 +6762,13 @@
         <v/>
       </c>
       <c r="O25" s="6">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>47</v>
@@ -6802,7 +6802,7 @@
         <v>1426.25</v>
       </c>
       <c r="AE25" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF25" s="5" t="s">
         <v>63</v>
@@ -6812,13 +6812,13 @@
       <c r="AI25" s="5"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL25" s="5" t="s">
         <v>96</v>
       </c>
       <c r="AM25" s="6">
-        <v>46217</v>
+        <v>46274</v>
       </c>
       <c r="AN25" s="5" t="s">
         <v>55</v>
@@ -6826,62 +6826,62 @@
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>584</v>
+        <v>90</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="4">
-        <v>565362589</v>
+        <v>562803289</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>549</v>
+        <v>92</v>
       </c>
       <c r="F26" s="6">
-        <v>46197</v>
+        <v>46191</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="K26" s="3">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="L26" s="11">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>-13</v>
-      </c>
-      <c r="M26" s="11">
-        <f ca="1">IF($F26="","",$F26+90-TODAY())</f>
-        <v>-13</v>
+        <v>-19</v>
+      </c>
+      <c r="M26" s="11" t="str">
+        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <v/>
       </c>
       <c r="N26" s="11" t="str">
         <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
         <v/>
       </c>
       <c r="O26" s="6">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>49</v>
@@ -6896,7 +6896,7 @@
         <v>50</v>
       </c>
       <c r="Z26" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -6906,26 +6906,26 @@
       </c>
       <c r="AC26" s="6"/>
       <c r="AD26" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE26" s="4">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF26" s="5" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="AG26" s="5"/>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AM26" s="6">
-        <v>46274</v>
+        <v>46217</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>55</v>
@@ -6933,62 +6933,62 @@
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>525</v>
+        <v>67</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>584</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="4">
-        <v>563477944</v>
+        <v>565362589</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>100</v>
+        <v>549</v>
       </c>
       <c r="F27" s="6">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="K27" s="3">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="L27" s="11">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>-12</v>
-      </c>
-      <c r="M27" s="11" t="str">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v/>
+        <v>-13</v>
+      </c>
+      <c r="M27" s="11">
+        <f ca="1">IF($F27="","",$F27+90-TODAY())</f>
+        <v>-13</v>
       </c>
       <c r="N27" s="11" t="str">
         <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
         <v/>
       </c>
       <c r="O27" s="6">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>49</v>
@@ -7003,7 +7003,7 @@
         <v>50</v>
       </c>
       <c r="Z27" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA27" s="7">
         <v>0</v>
@@ -7013,26 +7013,26 @@
       </c>
       <c r="AC27" s="6"/>
       <c r="AD27" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE27" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="AM27" s="6">
-        <v>46217</v>
+        <v>46274</v>
       </c>
       <c r="AN27" s="5" t="s">
         <v>55</v>
@@ -7040,49 +7040,47 @@
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>583</v>
-      </c>
-      <c r="C28" s="3">
-        <v>46259</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="4">
-        <v>563454979</v>
+        <v>563477944</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="F28" s="6">
         <v>46198</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="K28" s="3">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="L28" s="11">
         <f ca="1">IF($O28="","",$O28-TODAY())</f>
         <v>-12</v>
       </c>
-      <c r="M28" s="11">
+      <c r="M28" s="11" t="str">
+        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N28" s="11" t="str">
         <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>324</v>
-      </c>
-      <c r="N28" s="11">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>324</v>
+        <v/>
       </c>
       <c r="O28" s="6">
         <v>46288</v>
@@ -7091,10 +7089,10 @@
         <v>45</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S28" s="5" t="s">
         <v>48</v>
@@ -7112,7 +7110,7 @@
         <v>50</v>
       </c>
       <c r="Z28" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -7120,11 +7118,9 @@
       <c r="AB28" s="7">
         <v>0</v>
       </c>
-      <c r="AC28" s="6">
-        <v>46259</v>
-      </c>
+      <c r="AC28" s="6"/>
       <c r="AD28" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE28" s="4">
         <v>44</v>
@@ -7137,13 +7133,13 @@
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="AL28" s="5" t="s">
         <v>96</v>
       </c>
       <c r="AM28" s="6">
-        <v>46246</v>
+        <v>46217</v>
       </c>
       <c r="AN28" s="5" t="s">
         <v>55</v>
@@ -7151,64 +7147,64 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>564</v>
+        <v>67</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C29" s="3">
-        <v>46267</v>
+        <v>46259</v>
       </c>
       <c r="D29" s="4">
-        <v>563716478</v>
+        <v>563454979</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F29" s="6">
-        <v>46202</v>
+        <v>46198</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="K29" s="3">
-        <v>46275</v>
+        <v>46284</v>
       </c>
       <c r="L29" s="11">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="M29" s="11">
-        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
-        <v>-8</v>
+        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <v>324</v>
       </c>
       <c r="N29" s="11">
         <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O29" s="6">
-        <v>46292</v>
+        <v>46288</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>49</v>
@@ -7223,22 +7219,22 @@
         <v>50</v>
       </c>
       <c r="Z29" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA29" s="7">
-        <v>1281.58</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="7">
-        <v>173.48</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="6">
-        <v>46267</v>
+        <v>46259</v>
       </c>
       <c r="AD29" s="7">
-        <v>-28.81</v>
+        <v>1372.91</v>
       </c>
       <c r="AE29" s="4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>63</v>
@@ -7246,17 +7242,15 @@
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
-      <c r="AJ29" s="4" t="s">
-        <v>552</v>
-      </c>
+      <c r="AJ29" s="4"/>
       <c r="AK29" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AL29" s="5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AM29" s="6">
-        <v>46217</v>
+        <v>46246</v>
       </c>
       <c r="AN29" s="5" t="s">
         <v>55</v>
@@ -7264,65 +7258,67 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C30" s="3"/>
+        <v>564</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46267</v>
+      </c>
       <c r="D30" s="4">
-        <v>562674720</v>
+        <v>563716478</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>117</v>
+        <v>551</v>
       </c>
       <c r="F30" s="6">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>44</v>
       </c>
       <c r="K30" s="3">
-        <v>46300</v>
+        <v>46275</v>
       </c>
       <c r="L30" s="11">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>10</v>
-      </c>
-      <c r="M30" s="11" t="str">
-        <f ca="1">IF($C30="","",$C30+180-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N30" s="11" t="str">
-        <f ca="1">IF($C30="","",$C30+180-TODAY())</f>
-        <v/>
+        <v>-8</v>
+      </c>
+      <c r="M30" s="11">
+        <f ca="1">IF($F30="","",$F30+90-TODAY())</f>
+        <v>-8</v>
+      </c>
+      <c r="N30" s="11">
+        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
+        <v>332</v>
       </c>
       <c r="O30" s="6">
-        <v>46310</v>
+        <v>46292</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="R30" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T30" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U30" s="5" t="s">
         <v>48</v>
@@ -7337,30 +7333,34 @@
         <v>1426.25</v>
       </c>
       <c r="AA30" s="7">
-        <v>0</v>
+        <v>1281.58</v>
       </c>
       <c r="AB30" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="6"/>
+        <v>173.48</v>
+      </c>
+      <c r="AC30" s="6">
+        <v>46267</v>
+      </c>
       <c r="AD30" s="7">
-        <v>1426.25</v>
+        <v>-28.81</v>
       </c>
       <c r="AE30" s="4">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AF30" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG30" s="5"/>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
-      <c r="AJ30" s="4"/>
+      <c r="AJ30" s="4" t="s">
+        <v>552</v>
+      </c>
       <c r="AK30" s="5" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="AL30" s="5" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="AM30" s="6">
         <v>46217</v>
@@ -15231,65 +15231,67 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>564</v>
+        <v>523</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="C2" s="3">
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="D2" s="4">
-        <v>562573309</v>
+        <v>561704073</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>204</v>
+        <v>422</v>
       </c>
       <c r="F2" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>411</v>
+      </c>
+      <c r="K2" s="3">
+        <v>46300</v>
+      </c>
       <c r="L2" s="11">
         <f ca="1">IF($O2="","",$O2-TODAY())</f>
-        <v>-29</v>
+        <v>2</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
-        <v>-29</v>
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <v>86</v>
       </c>
       <c r="N2" s="11">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>262</v>
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <v>86</v>
       </c>
       <c r="O2" s="6">
-        <v>46271</v>
+        <v>46302</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>48</v>
@@ -15301,44 +15303,42 @@
         <v>50</v>
       </c>
       <c r="Z2" s="7">
-        <v>11163.74</v>
+        <v>2493.33</v>
       </c>
       <c r="AA2" s="7">
-        <v>0</v>
+        <v>2418.7399999999998</v>
       </c>
       <c r="AB2" s="7">
-        <v>0</v>
+        <v>67.13</v>
       </c>
       <c r="AC2" s="6">
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="AD2" s="7">
-        <v>11163.74</v>
+        <v>7.46</v>
       </c>
       <c r="AE2" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>293</v>
+        <v>222</v>
       </c>
       <c r="AG2" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="AI2" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="AJ2" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="4">
+        <v>565633590</v>
+      </c>
       <c r="AK2" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="AM2" s="6">
-        <v>46190</v>
+        <v>46184</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>376</v>
@@ -15346,65 +15346,65 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>572</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46197</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="4">
-        <v>562086355</v>
+        <v>563845926</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>399</v>
+        <v>253</v>
       </c>
       <c r="F3" s="6">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="K3" s="3"/>
+      <c r="J3" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K3" s="3">
+        <v>46300</v>
+      </c>
       <c r="L3" s="11">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>-26</v>
+        <v>18</v>
       </c>
       <c r="M3" s="11">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
-        <v>-26</v>
-      </c>
-      <c r="N3" s="11">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>262</v>
+        <f ca="1">IF($F3="","",$F3+365-TODAY())</f>
+        <v>263</v>
+      </c>
+      <c r="N3" s="11" t="str">
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v/>
       </c>
       <c r="O3" s="6">
-        <v>46274</v>
+        <v>46318</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>116</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>48</v>
@@ -15416,7 +15416,7 @@
         <v>50</v>
       </c>
       <c r="Z3" s="7">
-        <v>2493.33</v>
+        <v>14614.67</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -15424,88 +15424,94 @@
       <c r="AB3" s="7">
         <v>0</v>
       </c>
-      <c r="AC3" s="6">
-        <v>46197</v>
-      </c>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="7">
-        <v>2493.33</v>
+        <v>14614.67</v>
       </c>
       <c r="AE3" s="4">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>223</v>
+        <v>394</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
+        <v>293</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AM3" s="6">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>572</v>
+      </c>
       <c r="C4" s="3">
-        <v>46232</v>
+        <v>46197</v>
       </c>
       <c r="D4" s="4">
-        <v>564581824</v>
+        <v>562573309</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>558</v>
+        <v>204</v>
       </c>
       <c r="F4" s="6">
-        <v>46202</v>
+        <v>46181</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>475</v>
+        <v>98</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>475</v>
+        <v>98</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>559</v>
+        <v>392</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="11">
         <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v>52</v>
+        <v>-29</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">IF($F4="","",$F4+365-TODAY())</f>
-        <v>267</v>
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-29</v>
       </c>
       <c r="N4" s="11">
-        <f ca="1">IF($F4="","",$F4+365-TODAY())</f>
-        <v>267</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>262</v>
       </c>
       <c r="O4" s="6">
-        <v>46352</v>
+        <v>46271</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>476</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>477</v>
+        <v>99</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="S4" s="5" t="s">
         <v>116</v>
@@ -15514,7 +15520,7 @@
         <v>49</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -15523,94 +15529,104 @@
         <v>50</v>
       </c>
       <c r="Z4" s="7">
-        <v>3471.16</v>
+        <v>11163.74</v>
       </c>
       <c r="AA4" s="7">
-        <v>3230.34</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="7">
-        <v>433.48</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46232</v>
+        <v>46197</v>
       </c>
       <c r="AD4" s="7">
-        <v>-192.66</v>
+        <v>11163.74</v>
       </c>
       <c r="AE4" s="4">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
+        <v>293</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>391</v>
+      </c>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>561</v>
+        <v>62</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AM4" s="6">
-        <v>46217</v>
+        <v>46190</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>572</v>
+      </c>
       <c r="C5" s="3">
-        <v>46253</v>
+        <v>46197</v>
       </c>
       <c r="D5" s="4">
-        <v>564529714</v>
+        <v>562086355</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="F5" s="6">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>563</v>
+      <c r="J5" s="14" t="s">
+        <v>400</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="11">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>75</v>
+        <v>-26</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">IF($F5="","",$F5+365-TODAY())</f>
-        <v>260</v>
+        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <v>-26</v>
       </c>
       <c r="N5" s="11">
-        <f ca="1">IF($F5="","",$F5+365-TODAY())</f>
-        <v>260</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>262</v>
       </c>
       <c r="O5" s="6">
-        <v>46375</v>
+        <v>46274</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="S5" s="5" t="s">
         <v>116</v>
@@ -15619,7 +15635,7 @@
         <v>49</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -15628,7 +15644,7 @@
         <v>50</v>
       </c>
       <c r="Z5" s="7">
-        <v>17815.21</v>
+        <v>2493.33</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -15637,35 +15653,31 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46253</v>
+        <v>46197</v>
       </c>
       <c r="AD5" s="7">
-        <v>17815.21</v>
+        <v>2493.33</v>
       </c>
       <c r="AE5" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AH5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI5" s="5" t="s">
-        <v>293</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>427</v>
+        <v>312</v>
       </c>
       <c r="AM5" s="6">
-        <v>46246</v>
+        <v>46188</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>376</v>
@@ -15675,104 +15687,102 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="D6" s="4">
-        <v>561270366</v>
+        <v>564581824</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>279</v>
+        <v>558</v>
       </c>
       <c r="F6" s="6">
-        <v>46177</v>
+        <v>46202</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>120</v>
+        <v>475</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>120</v>
+        <v>475</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>280</v>
+        <v>65</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>406</v>
+        <v>559</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="11">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>253</v>
+        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
+        <v>267</v>
       </c>
       <c r="N6" s="11">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
-        <v>8</v>
+        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
+        <v>267</v>
       </c>
       <c r="O6" s="6">
-        <v>46542</v>
+        <v>46352</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>49</v>
+        <v>476</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>121</v>
+        <v>477</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>323</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z6" s="7">
-        <v>5614.63</v>
+        <v>3471.16</v>
       </c>
       <c r="AA6" s="7">
-        <v>0</v>
+        <v>3230.34</v>
       </c>
       <c r="AB6" s="7">
-        <v>0</v>
+        <v>433.48</v>
       </c>
       <c r="AC6" s="6">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="AD6" s="7">
-        <v>5614.63</v>
+        <v>-192.66</v>
       </c>
       <c r="AE6" s="4">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>186</v>
+        <v>560</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>58</v>
+        <v>561</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>312</v>
       </c>
       <c r="AM6" s="6">
-        <v>46181</v>
+        <v>46217</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>376</v>
@@ -15782,62 +15792,62 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3">
+        <v>46253</v>
+      </c>
+      <c r="D7" s="4">
+        <v>564529714</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F7" s="6">
         <v>46195</v>
       </c>
-      <c r="D7" s="4">
-        <v>562554208</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46188</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>432</v>
+        <v>43</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>433</v>
+        <v>563</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="11">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
         <v>260</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
-        <v>15</v>
+        <f ca="1">IF($F7="","",$F7+365-TODAY())</f>
+        <v>260</v>
       </c>
       <c r="O7" s="6">
-        <v>46553</v>
+        <v>46375</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -15846,7 +15856,7 @@
         <v>50</v>
       </c>
       <c r="Z7" s="7">
-        <v>5784.24</v>
+        <v>17815.21</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -15855,31 +15865,35 @@
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46195</v>
+        <v>46253</v>
       </c>
       <c r="AD7" s="7">
-        <v>5784.24</v>
+        <v>17815.21</v>
       </c>
       <c r="AE7" s="4">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="5"/>
+        <v>260</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI7" s="5" t="s">
+        <v>293</v>
+      </c>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>95</v>
+        <v>262</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="AM7" s="6">
-        <v>46190</v>
+        <v>46246</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>376</v>
@@ -15889,16 +15903,16 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="D8" s="4">
-        <v>564087324</v>
+        <v>561270366</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>435</v>
+        <v>279</v>
       </c>
       <c r="F8" s="6">
-        <v>46191</v>
+        <v>46177</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>120</v>
@@ -15907,7 +15921,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>406</v>
@@ -15915,18 +15929,18 @@
       <c r="K8" s="3"/>
       <c r="L8" s="11">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="M8" s="11">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="N8" s="11">
         <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="O8" s="6">
-        <v>46556</v>
+        <v>46542</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>49</v>
@@ -15964,13 +15978,13 @@
         <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="AD8" s="7">
         <v>5614.63</v>
       </c>
       <c r="AE8" s="4">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AF8" s="5" t="s">
         <v>186</v>
@@ -15980,63 +15994,79 @@
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="AM8" s="6">
-        <v>46210</v>
+        <v>46181</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="C9" s="3"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3">
+        <v>46195</v>
+      </c>
       <c r="D9" s="4">
-        <v>563830748</v>
+        <v>562554208</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>297</v>
+        <v>431</v>
       </c>
       <c r="F9" s="6">
-        <v>46193</v>
+        <v>46188</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>43</v>
+        <v>432</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="11" t="str">
+      <c r="L9" s="11">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="M9" s="11">
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>260</v>
+      </c>
+      <c r="N9" s="11">
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>15</v>
+      </c>
+      <c r="O9" s="6">
+        <v>46553</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="Q9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
@@ -16044,7 +16074,7 @@
         <v>50</v>
       </c>
       <c r="Z9" s="7">
-        <v>11094.23</v>
+        <v>5784.24</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -16052,25 +16082,23 @@
       <c r="AB9" s="7">
         <v>0</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="6">
+        <v>46195</v>
+      </c>
       <c r="AD9" s="7">
-        <v>11094.23</v>
+        <v>5784.24</v>
       </c>
       <c r="AE9" s="4">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>437</v>
+        <v>223</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="AI9" s="5" t="s">
-        <v>438</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
         <v>95</v>
@@ -16079,7 +16107,7 @@
         <v>327</v>
       </c>
       <c r="AM9" s="6">
-        <v>46203</v>
+        <v>46190</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>376</v>
@@ -16088,52 +16116,74 @@
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>46218</v>
+      </c>
       <c r="D10" s="4">
-        <v>564560469</v>
+        <v>564087324</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F10" s="6">
-        <v>46202</v>
+        <v>46191</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="11" t="str">
+      <c r="L10" s="11">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="5"/>
+        <v>256</v>
+      </c>
+      <c r="M10" s="11">
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>283</v>
+      </c>
+      <c r="N10" s="11">
+        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <v>38</v>
+      </c>
+      <c r="O10" s="6">
+        <v>46556</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="Q10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="Z10" s="7">
-        <v>15998.71</v>
+        <v>5614.63</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -16141,26 +16191,24 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="6">
+        <v>46218</v>
+      </c>
       <c r="AD10" s="7">
-        <v>15998.71</v>
+        <v>5614.63</v>
       </c>
       <c r="AE10" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>441</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>327</v>
@@ -16174,71 +16222,49 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>564</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46256</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="4">
-        <v>562557056</v>
+        <v>563830748</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>378</v>
+        <v>297</v>
       </c>
       <c r="F11" s="6">
-        <v>46174</v>
+        <v>46193</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="K11" s="3">
-        <v>46272</v>
-      </c>
-      <c r="L11" s="11">
+        <v>436</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="11" t="str">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>-36</v>
-      </c>
-      <c r="M11" s="11">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
-        <v>136</v>
-      </c>
-      <c r="N11" s="11">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>321</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46264</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="5"/>
       <c r="Q11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
@@ -16246,7 +16272,7 @@
         <v>50</v>
       </c>
       <c r="Z11" s="7">
-        <v>9056.39</v>
+        <v>11094.23</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -16256,112 +16282,86 @@
       </c>
       <c r="AC11" s="6"/>
       <c r="AD11" s="7">
-        <v>9056.39</v>
+        <v>11094.23</v>
       </c>
       <c r="AE11" s="4">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>260</v>
+        <v>437</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>176</v>
+        <v>293</v>
       </c>
       <c r="AH11" s="5" t="s">
         <v>379</v>
       </c>
       <c r="AI11" s="5" t="s">
-        <v>261</v>
+        <v>438</v>
       </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM11" s="6">
-        <v>46190</v>
+        <v>46203</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" s="3">
-        <v>46254</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="4">
-        <v>562559783</v>
+        <v>564560469</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="F12" s="6">
-        <v>46177</v>
+        <v>46202</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="K12" s="3">
-        <v>46272</v>
-      </c>
-      <c r="L12" s="11">
+        <v>440</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="11" t="str">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>-33</v>
-      </c>
-      <c r="M12" s="11">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
-        <v>134</v>
-      </c>
-      <c r="N12" s="11">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>319</v>
-      </c>
-      <c r="O12" s="6">
-        <v>46267</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="5"/>
       <c r="Q12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U12" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="Z12" s="7">
-        <v>9056.39</v>
+        <v>15998.71</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -16369,36 +16369,32 @@
       <c r="AB12" s="7">
         <v>0</v>
       </c>
-      <c r="AC12" s="6">
-        <v>46197</v>
-      </c>
+      <c r="AC12" s="6"/>
       <c r="AD12" s="7">
-        <v>9056.39</v>
+        <v>15998.71</v>
       </c>
       <c r="AE12" s="4">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AF12" s="5" t="s">
         <v>176</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="AH12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI12" s="5" t="s">
-        <v>383</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="AL12" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM12" s="6">
-        <v>46190</v>
+        <v>46210</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>376</v>
@@ -16406,59 +16402,61 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C13" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46256</v>
+      </c>
       <c r="D13" s="4">
-        <v>570979198</v>
+        <v>562557056</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F13" s="6">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="K13" s="3">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="L13" s="11">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>-29</v>
-      </c>
-      <c r="M13" s="11" t="str">
+        <v>-36</v>
+      </c>
+      <c r="M13" s="11">
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>136</v>
+      </c>
+      <c r="N13" s="11">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N13" s="11" t="str">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v/>
+        <v>321</v>
       </c>
       <c r="O13" s="6">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>48</v>
@@ -16469,16 +16467,14 @@
       <c r="U13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V13" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="V13" s="5"/>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z13" s="7">
-        <v>20158.46</v>
+        <v>9056.39</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -16488,22 +16484,22 @@
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" s="7">
-        <v>20158.46</v>
+        <v>9056.39</v>
       </c>
       <c r="AE13" s="4">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>388</v>
+        <v>260</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>389</v>
+        <v>176</v>
       </c>
       <c r="AH13" s="5" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="AI13" s="5" t="s">
-        <v>391</v>
+        <v>261</v>
       </c>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
@@ -16524,80 +16520,76 @@
         <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C14" s="3">
-        <v>46236</v>
+        <v>46254</v>
       </c>
       <c r="D14" s="4">
-        <v>562578639</v>
+        <v>562559783</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="F14" s="6">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="K14" s="3">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="L14" s="11">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>-29</v>
+        <v>-33</v>
       </c>
       <c r="M14" s="11">
-        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
-        <v>-29</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>134</v>
       </c>
       <c r="N14" s="11">
-        <f ca="1">IF($C14="","",$C14+540-TODAY())</f>
-        <v>476</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>319</v>
       </c>
       <c r="O14" s="6">
-        <v>46271</v>
+        <v>46267</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>341</v>
+        <v>46</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>542</v>
+        <v>49</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V14" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="W14" s="5" t="s">
-        <v>323</v>
-      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z14" s="7">
-        <v>25252.06</v>
+        <v>9056.39</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -16605,24 +16597,26 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="6">
+        <v>46197</v>
+      </c>
       <c r="AD14" s="7">
-        <v>25252.06</v>
+        <v>9056.39</v>
       </c>
       <c r="AE14" s="4">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AF14" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH14" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="AG14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AH14" s="5" t="s">
-        <v>398</v>
-      </c>
       <c r="AI14" s="5" t="s">
-        <v>260</v>
+        <v>383</v>
       </c>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
@@ -16640,61 +16634,59 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C15" s="3">
-        <v>46197</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="4">
-        <v>570992408</v>
+        <v>570979198</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>208</v>
+        <v>385</v>
       </c>
       <c r="F15" s="6">
-        <v>46185</v>
+        <v>46181</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="K15" s="3">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="L15" s="11">
         <f ca="1">IF($O15="","",$O15-TODAY())</f>
-        <v>-25</v>
-      </c>
-      <c r="M15" s="11">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>77</v>
-      </c>
-      <c r="N15" s="11">
+        <v>-29</v>
+      </c>
+      <c r="M15" s="11" t="str">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>262</v>
+        <v/>
+      </c>
+      <c r="N15" s="11" t="str">
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v/>
       </c>
       <c r="O15" s="6">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>48</v>
@@ -16705,14 +16697,16 @@
       <c r="U15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V15" s="5"/>
+      <c r="V15" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z15" s="7">
-        <v>5614.63</v>
+        <v>20158.46</v>
       </c>
       <c r="AA15" s="7">
         <v>0</v>
@@ -16720,30 +16714,34 @@
       <c r="AB15" s="7">
         <v>0</v>
       </c>
-      <c r="AC15" s="6">
-        <v>46197</v>
-      </c>
+      <c r="AC15" s="6"/>
       <c r="AD15" s="7">
-        <v>5614.63</v>
+        <v>20158.46</v>
       </c>
       <c r="AE15" s="4">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG15" s="5"/>
-      <c r="AH15" s="5"/>
-      <c r="AI15" s="5"/>
+        <v>388</v>
+      </c>
+      <c r="AG15" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="AH15" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="AI15" s="5" t="s">
+        <v>391</v>
+      </c>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AL15" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM15" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="AN15" s="5" t="s">
         <v>376</v>
@@ -16751,65 +16749,67 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>395</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46236</v>
+      </c>
       <c r="D16" s="4">
-        <v>571013418</v>
+        <v>562578639</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>219</v>
+        <v>396</v>
       </c>
       <c r="F16" s="6">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>93</v>
+        <v>339</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>93</v>
+        <v>339</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="K16" s="3">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="L16" s="11">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>-19</v>
-      </c>
-      <c r="M16" s="11" t="str">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N16" s="11" t="str">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v/>
+        <v>-29</v>
+      </c>
+      <c r="M16" s="11">
+        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
+        <v>-29</v>
+      </c>
+      <c r="N16" s="11">
+        <f ca="1">IF($C16="","",$C16+540-TODAY())</f>
+        <v>476</v>
       </c>
       <c r="O16" s="6">
-        <v>46281</v>
+        <v>46271</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>94</v>
+        <v>341</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>49</v>
+        <v>542</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>48</v>
@@ -16817,13 +16817,15 @@
       <c r="V16" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="X16" s="5"/>
       <c r="Y16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z16" s="7">
-        <v>15769.79</v>
+        <v>25252.06</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -16833,30 +16835,32 @@
       </c>
       <c r="AC16" s="6"/>
       <c r="AD16" s="7">
-        <v>15769.79</v>
+        <v>25252.06</v>
       </c>
       <c r="AE16" s="4">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>293</v>
+        <v>201</v>
       </c>
       <c r="AG16" s="5" t="s">
-        <v>409</v>
+        <v>176</v>
       </c>
       <c r="AH16" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="AI16" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="AI16" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>95</v>
+        <v>262</v>
       </c>
       <c r="AL16" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM16" s="6">
-        <v>46210</v>
+        <v>46190</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>376</v>
@@ -16866,20 +16870,20 @@
       <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>520</v>
+      <c r="B17" s="13" t="s">
+        <v>404</v>
       </c>
       <c r="C17" s="3">
-        <v>46272</v>
+        <v>46197</v>
       </c>
       <c r="D17" s="4">
-        <v>563839702</v>
+        <v>570992408</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>413</v>
+        <v>208</v>
       </c>
       <c r="F17" s="6">
-        <v>46197</v>
+        <v>46185</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>42</v>
@@ -16888,28 +16892,28 @@
         <v>42</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="K17" s="3">
-        <v>46282</v>
+        <v>46271</v>
       </c>
       <c r="L17" s="11">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>-13</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="11">
         <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="N17" s="11">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="O17" s="6">
-        <v>46287</v>
+        <v>46275</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>45</v>
@@ -16936,7 +16940,7 @@
         <v>50</v>
       </c>
       <c r="Z17" s="7">
-        <v>10892.84</v>
+        <v>5614.63</v>
       </c>
       <c r="AA17" s="7">
         <v>0</v>
@@ -16944,32 +16948,30 @@
       <c r="AB17" s="7">
         <v>0</v>
       </c>
-      <c r="AC17" s="6"/>
+      <c r="AC17" s="6">
+        <v>46197</v>
+      </c>
       <c r="AD17" s="7">
-        <v>10892.84</v>
+        <v>5614.63</v>
       </c>
       <c r="AE17" s="4">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG17" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH17" s="5" t="s">
-        <v>415</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="AG17" s="5"/>
+      <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM17" s="6">
-        <v>46203</v>
+        <v>46189</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>376</v>
@@ -16979,37 +16981,37 @@
       <c r="A18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>524</v>
+      <c r="B18" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4">
-        <v>572208778</v>
+        <v>571013418</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="F18" s="6">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>247</v>
+        <v>93</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>247</v>
+        <v>93</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="K18" s="3">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="L18" s="11">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="M18" s="11" t="str">
         <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
@@ -17020,7 +17022,7 @@
         <v/>
       </c>
       <c r="O18" s="6">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>45</v>
@@ -17040,14 +17042,16 @@
       <c r="U18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V18" s="5"/>
+      <c r="V18" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z18" s="7">
-        <v>11163.74</v>
+        <v>15769.79</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -17055,27 +17059,23 @@
       <c r="AB18" s="7">
         <v>0</v>
       </c>
-      <c r="AC18" s="6">
-        <v>46220</v>
-      </c>
+      <c r="AC18" s="6"/>
       <c r="AD18" s="7">
-        <v>11163.74</v>
+        <v>15769.79</v>
       </c>
       <c r="AE18" s="4">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>394</v>
+        <v>293</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
       <c r="AH18" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI18" s="5" t="s">
-        <v>417</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
         <v>95</v>
@@ -17084,7 +17084,7 @@
         <v>327</v>
       </c>
       <c r="AM18" s="6">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>376</v>
@@ -17094,56 +17094,56 @@
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>526</v>
+      <c r="B19" s="2" t="s">
+        <v>520</v>
       </c>
       <c r="C19" s="3">
-        <v>46210</v>
+        <v>46272</v>
       </c>
       <c r="D19" s="4">
-        <v>563854100</v>
+        <v>563839702</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>242</v>
+        <v>413</v>
       </c>
       <c r="F19" s="6">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="K19" s="3">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="L19" s="11">
         <f ca="1">IF($O19="","",$O19-TODAY())</f>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="M19" s="11">
         <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="N19" s="11">
         <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
-        <v>275</v>
+        <v>337</v>
       </c>
       <c r="O19" s="6">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="R19" s="5" t="s">
         <v>47</v>
@@ -17157,16 +17157,14 @@
       <c r="U19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V19" s="5" t="s">
-        <v>323</v>
-      </c>
+      <c r="V19" s="5"/>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z19" s="7">
-        <v>6297.27</v>
+        <v>10892.84</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -17176,10 +17174,10 @@
       </c>
       <c r="AC19" s="6"/>
       <c r="AD19" s="7">
-        <v>6297.27</v>
+        <v>10892.84</v>
       </c>
       <c r="AE19" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF19" s="5" t="s">
         <v>176</v>
@@ -17188,12 +17186,12 @@
         <v>201</v>
       </c>
       <c r="AH19" s="5" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>95</v>
+        <v>262</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>327</v>
@@ -17207,67 +17205,65 @@
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>591</v>
-      </c>
-      <c r="C20" s="3">
-        <v>46223</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="4">
-        <v>563941508</v>
+        <v>572208778</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>420</v>
+        <v>246</v>
       </c>
       <c r="F20" s="6">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="K20" s="3">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="L20" s="11">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v>-7</v>
-      </c>
-      <c r="M20" s="11">
-        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
-        <v>-7</v>
-      </c>
-      <c r="N20" s="11">
+        <v>-12</v>
+      </c>
+      <c r="M20" s="11" t="str">
         <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>103</v>
+        <v/>
+      </c>
+      <c r="N20" s="11" t="str">
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <v/>
       </c>
       <c r="O20" s="6">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U20" s="5" t="s">
         <v>48</v>
@@ -17279,7 +17275,7 @@
         <v>50</v>
       </c>
       <c r="Z20" s="7">
-        <v>2493.33</v>
+        <v>11163.74</v>
       </c>
       <c r="AA20" s="7">
         <v>0</v>
@@ -17288,31 +17284,35 @@
         <v>0</v>
       </c>
       <c r="AC20" s="6">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="AD20" s="7">
-        <v>2493.33</v>
+        <v>11163.74</v>
       </c>
       <c r="AE20" s="4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>222</v>
+        <v>394</v>
       </c>
       <c r="AG20" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
+        <v>293</v>
+      </c>
+      <c r="AH20" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="AI20" s="5" t="s">
+        <v>417</v>
+      </c>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AM20" s="6">
-        <v>46213</v>
+        <v>46203</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>376</v>
@@ -17323,58 +17323,58 @@
         <v>67</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="C21" s="3">
-        <v>46265</v>
+        <v>46210</v>
       </c>
       <c r="D21" s="4">
-        <v>564121445</v>
+        <v>563854100</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>421</v>
+        <v>242</v>
       </c>
       <c r="F21" s="6">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="K21" s="3">
-        <v>46259</v>
+        <v>46283</v>
       </c>
       <c r="L21" s="11">
         <f ca="1">IF($O21="","",$O21-TODAY())</f>
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="M21" s="11">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>330</v>
+        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <v>90</v>
       </c>
       <c r="N21" s="11">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>330</v>
+        <v>275</v>
       </c>
       <c r="O21" s="6">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S21" s="5" t="s">
         <v>48</v>
@@ -17394,7 +17394,7 @@
         <v>50</v>
       </c>
       <c r="Z21" s="7">
-        <v>5614.63</v>
+        <v>6297.27</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -17404,26 +17404,30 @@
       </c>
       <c r="AC21" s="6"/>
       <c r="AD21" s="7">
-        <v>5614.63</v>
+        <v>6297.27</v>
       </c>
       <c r="AE21" s="4">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
+        <v>176</v>
+      </c>
+      <c r="AG21" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH21" s="5" t="s">
+        <v>419</v>
+      </c>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AL21" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM21" s="6">
-        <v>46211</v>
+        <v>46203</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>376</v>
@@ -17431,64 +17435,64 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>598</v>
+        <v>67</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>591</v>
       </c>
       <c r="C22" s="3">
-        <v>46206</v>
+        <v>46223</v>
       </c>
       <c r="D22" s="4">
-        <v>561704073</v>
+        <v>563941508</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F22" s="6">
-        <v>46182</v>
+        <v>46203</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>411</v>
       </c>
       <c r="K22" s="3">
-        <v>46300</v>
+        <v>46284</v>
       </c>
       <c r="L22" s="11">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="M22" s="11">
-        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>86</v>
+        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <v>-7</v>
       </c>
       <c r="N22" s="11">
         <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="O22" s="6">
-        <v>46302</v>
+        <v>46293</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>47</v>
@@ -17506,39 +17510,37 @@
         <v>2493.33</v>
       </c>
       <c r="AA22" s="7">
-        <v>2418.7399999999998</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="7">
-        <v>67.13</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="6">
-        <v>46206</v>
+        <v>46223</v>
       </c>
       <c r="AD22" s="7">
-        <v>7.46</v>
+        <v>2493.33</v>
       </c>
       <c r="AE22" s="4">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>222</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="4">
-        <v>565633590</v>
-      </c>
+      <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="AL22" s="5" t="s">
         <v>312</v>
       </c>
       <c r="AM22" s="6">
-        <v>46184</v>
+        <v>46213</v>
       </c>
       <c r="AN22" s="5" t="s">
         <v>376</v>
@@ -17546,77 +17548,81 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C23" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46265</v>
+      </c>
       <c r="D23" s="4">
-        <v>563845926</v>
+        <v>564121445</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>253</v>
+        <v>421</v>
       </c>
       <c r="F23" s="6">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="K23" s="3">
-        <v>46300</v>
+        <v>46259</v>
       </c>
       <c r="L23" s="11">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>18</v>
+        <v>-7</v>
       </c>
       <c r="M23" s="11">
-        <f ca="1">IF($F23="","",$F23+365-TODAY())</f>
-        <v>263</v>
-      </c>
-      <c r="N23" s="11" t="str">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v/>
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>330</v>
+      </c>
+      <c r="N23" s="11">
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>330</v>
       </c>
       <c r="O23" s="6">
-        <v>46318</v>
+        <v>46293</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="R23" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V23" s="5"/>
+      <c r="V23" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z23" s="7">
-        <v>14614.67</v>
+        <v>5614.63</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -17626,32 +17632,26 @@
       </c>
       <c r="AC23" s="6"/>
       <c r="AD23" s="7">
-        <v>14614.67</v>
+        <v>5614.63</v>
       </c>
       <c r="AE23" s="4">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="AG23" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="AH23" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI23" s="5" t="s">
-        <v>430</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
+      <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AL23" s="5" t="s">
         <v>327</v>
       </c>
       <c r="AM23" s="6">
-        <v>46203</v>
+        <v>46211</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>376</v>
@@ -20374,7 +20374,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>575</v>
       </c>

--- a/SPC26S1 - 06 June.xlsx
+++ b/SPC26S1 - 06 June.xlsx
@@ -21,7 +21,7 @@
     <sheet name="Read Me" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AN$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DME!$A$1:$AO$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GAE!$A$1:$AO$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$31</definedName>
@@ -2732,7 +2732,7 @@
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
   <si>
-    <t>136 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+    <t>134 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">    1 - Due in 5 days or less: 19</t>
   </si>
   <si>
-    <t xml:space="preserve">    2 - Due in 6-30 days: 22</t>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 20</t>
   </si>
   <si>
     <t xml:space="preserve">    3 - Due in 31+ days: 36</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">    5 - No limit on file: 15</t>
   </si>
   <si>
-    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>Awaiting resolution on claim #556349314 (DOS 01/27/2026) before reprocessing</t>
@@ -4296,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7707,64 +7707,64 @@
         <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>596</v>
       </c>
       <c r="C34" s="3">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="D34" s="4">
-        <v>562882369</v>
+        <v>562803163</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>553</v>
+        <v>159</v>
       </c>
       <c r="F34" s="6">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="K34" s="3">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="L34" s="11">
         <f ca="1">IF($O34="","",$O34-TODAY())</f>
-        <v>12</v>
+        <v>-20</v>
       </c>
       <c r="M34" s="11">
-        <f ca="1">IF($C34="","",$C34+180-TODAY())</f>
-        <v>155</v>
+        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
+        <v>347</v>
       </c>
       <c r="N34" s="11">
-        <f ca="1">IF($C34="","",$C34+180-TODAY())</f>
-        <v>155</v>
+        <f ca="1">IF($C34="","",$C34+365-TODAY())</f>
+        <v>347</v>
       </c>
       <c r="O34" s="6">
-        <v>46312</v>
+        <v>46280</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S34" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T34" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U34" s="5" t="s">
         <v>48</v>
@@ -7776,7 +7776,7 @@
         <v>50</v>
       </c>
       <c r="Z34" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA34" s="7">
         <v>0</v>
@@ -7786,145 +7786,36 @@
       </c>
       <c r="AC34" s="6"/>
       <c r="AD34" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE34" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AF34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG34" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="AG34" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="AH34" s="5"/>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="AL34" s="5" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="AM34" s="6">
-        <v>46273</v>
+        <v>46217</v>
       </c>
       <c r="AN34" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C35" s="3">
-        <v>46282</v>
-      </c>
-      <c r="D35" s="4">
-        <v>562803163</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" s="6">
-        <v>46190</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K35" s="3">
-        <v>46293</v>
-      </c>
-      <c r="L35" s="11">
-        <f ca="1">IF($O35="","",$O35-TODAY())</f>
-        <v>-20</v>
-      </c>
-      <c r="M35" s="11">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
-        <v>347</v>
-      </c>
-      <c r="N35" s="11">
-        <f ca="1">IF($C35="","",$C35+365-TODAY())</f>
-        <v>347</v>
-      </c>
-      <c r="O35" s="6">
-        <v>46280</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S35" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U35" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V35" s="5"/>
-      <c r="W35" s="5"/>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z35" s="7">
-        <v>1372.91</v>
-      </c>
-      <c r="AA35" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="6"/>
-      <c r="AD35" s="7">
-        <v>1372.91</v>
-      </c>
-      <c r="AE35" s="4">
-        <v>52</v>
-      </c>
-      <c r="AF35" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG35" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH35" s="5"/>
-      <c r="AI35" s="5"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL35" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM35" s="6">
-        <v>46217</v>
-      </c>
-      <c r="AN35" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN35" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="L2:L35">
+  <autoFilter ref="A1:AN34" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:L34">
     <cfRule type="expression" dxfId="94" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -7941,7 +7832,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M35">
+  <conditionalFormatting sqref="M2:M34">
     <cfRule type="expression" dxfId="89" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -7958,7 +7849,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N35">
+  <conditionalFormatting sqref="N2:N34">
     <cfRule type="expression" dxfId="84" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -7975,7 +7866,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O35">
+  <conditionalFormatting sqref="O2:O34">
     <cfRule type="expression" dxfId="79" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -8019,7 +7910,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15067,7 +14958,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -17886,76 +17777,78 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>41</v>
+        <v>599</v>
       </c>
       <c r="C26" s="3">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="D26" s="4">
-        <v>563836350</v>
+        <v>563945778</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F26" s="6">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>295</v>
+        <v>105</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>295</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="K26" s="3">
-        <v>46290</v>
+        <v>46300</v>
       </c>
       <c r="L26" s="11">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M26" s="11">
-        <f ca="1">IF($F26="","",$F26+365-TODAY())</f>
-        <v>250</v>
+        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <v>97</v>
       </c>
       <c r="N26" s="11">
-        <f ca="1">IF($F26="","",$F26+365-TODAY())</f>
-        <v>250</v>
+        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <v>97</v>
       </c>
       <c r="O26" s="6">
-        <v>46305</v>
+        <v>46313</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>106</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>425</v>
+        <v>107</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="T26" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="V26" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="V26" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Z26" s="7">
-        <v>1758.12</v>
+        <v>7623.07</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -17964,152 +17857,37 @@
         <v>0</v>
       </c>
       <c r="AC26" s="6">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="AD26" s="7">
-        <v>1758.12</v>
+        <v>7623.07</v>
       </c>
       <c r="AE26" s="4">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AF26" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="AG26" s="5" t="s">
-        <v>394</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AG26" s="5"/>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>375</v>
+        <v>75</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>426</v>
+        <v>327</v>
       </c>
       <c r="AM26" s="6">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C27" s="3">
-        <v>46217</v>
-      </c>
-      <c r="D27" s="4">
-        <v>563945778</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46193</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="K27" s="3">
-        <v>46300</v>
-      </c>
-      <c r="L27" s="11">
-        <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>13</v>
-      </c>
-      <c r="M27" s="11">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>97</v>
-      </c>
-      <c r="N27" s="11">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>97</v>
-      </c>
-      <c r="O27" s="6">
-        <v>46313</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V27" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z27" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AA27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="6">
-        <v>46217</v>
-      </c>
-      <c r="AD27" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AE27" s="4">
-        <v>49</v>
-      </c>
-      <c r="AF27" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG27" s="5"/>
-      <c r="AH27" s="5"/>
-      <c r="AI27" s="5"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL27" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="AM27" s="6">
-        <v>46205</v>
-      </c>
-      <c r="AN27" s="5" t="s">
-        <v>376</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN27" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="L2:L27">
+  <autoFilter ref="A1:AN26" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -18126,7 +17904,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="34" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -18143,7 +17921,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="expression" dxfId="29" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -18160,7 +17938,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
